--- a/db/A7XLK-1111-HouseApp2.xlsx
+++ b/db/A7XLK-1111-HouseApp2.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1206744-55FF-CD49-9008-3EC4AD5E92F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61FC937-A106-1C45-9155-58C6E45752B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="640" yWindow="580" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
+    <workbookView xWindow="320" yWindow="1720" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId1"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="46" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="1217">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4485,6 +4489,183 @@
   <si>
     <t>2214坪</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>列標籤</t>
+  </si>
+  <si>
+    <t>101 和發大境</t>
+  </si>
+  <si>
+    <t>102 鴻典</t>
+  </si>
+  <si>
+    <t>103 樂捷市</t>
+  </si>
+  <si>
+    <t>104 奇幻莊園</t>
+  </si>
+  <si>
+    <t>105 樂田田</t>
+  </si>
+  <si>
+    <t>106 玉子園</t>
+  </si>
+  <si>
+    <t>107 台北國際村</t>
+  </si>
+  <si>
+    <t>108 豐邑氧森</t>
+  </si>
+  <si>
+    <t>201 富宇上城</t>
+  </si>
+  <si>
+    <t>202 禾悅花園</t>
+  </si>
+  <si>
+    <t>203 耀台北</t>
+  </si>
+  <si>
+    <t>204 皇普MVP</t>
+  </si>
+  <si>
+    <t>205 富宇敦峰</t>
+  </si>
+  <si>
+    <t>206 玄泰V1</t>
+  </si>
+  <si>
+    <t>207 和耀恆美</t>
+  </si>
+  <si>
+    <t>301 允將大作</t>
+  </si>
+  <si>
+    <t>302 欣時代</t>
+  </si>
+  <si>
+    <t>303 新潤翡麗</t>
+  </si>
+  <si>
+    <t>304 新潤鉑麗</t>
+  </si>
+  <si>
+    <t>305 根津苑</t>
+  </si>
+  <si>
+    <t>306 華悅城</t>
+  </si>
+  <si>
+    <t>307 富宇悅峰</t>
+  </si>
+  <si>
+    <t>308 合遠新天地</t>
+  </si>
+  <si>
+    <t>309 友文化</t>
+  </si>
+  <si>
+    <t>310 水悅青青</t>
+  </si>
+  <si>
+    <t>311 文華天際</t>
+  </si>
+  <si>
+    <t>312 君邑羅浮</t>
+  </si>
+  <si>
+    <t>313 大亮時代A7</t>
+  </si>
+  <si>
+    <t>314 大亮 泊</t>
+  </si>
+  <si>
+    <t>401 竹城甲子園</t>
+  </si>
+  <si>
+    <t>402 金捷市</t>
+  </si>
+  <si>
+    <t>403 捷市達</t>
+  </si>
+  <si>
+    <t>404 詠勝市中欣</t>
+  </si>
+  <si>
+    <t>405 新A7</t>
+  </si>
+  <si>
+    <t>406 富御捷境</t>
+  </si>
+  <si>
+    <t>407 富宇哈佛苑</t>
+  </si>
+  <si>
+    <t>408 頤昌豐岳</t>
+  </si>
+  <si>
+    <t>409 新未來2</t>
+  </si>
+  <si>
+    <t>410 新未來3</t>
+  </si>
+  <si>
+    <t>411 和洲金剛</t>
+  </si>
+  <si>
+    <t>412 君邑丘比特</t>
+  </si>
+  <si>
+    <t>413 頤昌璞岳</t>
+  </si>
+  <si>
+    <t>414 合謙學</t>
+  </si>
+  <si>
+    <t>416 維特魯威</t>
+  </si>
+  <si>
+    <t>417 頤昌澄岳</t>
+  </si>
+  <si>
+    <t>418 玄泰T1</t>
+  </si>
+  <si>
+    <t>501 新未來1</t>
+  </si>
+  <si>
+    <t>502 富宇天匯</t>
+  </si>
+  <si>
+    <t>503 竹城明治</t>
+  </si>
+  <si>
+    <t>504 竹城宇治</t>
+  </si>
+  <si>
+    <t>505 櫻花澍</t>
+  </si>
+  <si>
+    <t>506 和煦隆陞</t>
+  </si>
+  <si>
+    <t>511 遠雄文青</t>
+  </si>
+  <si>
+    <t>512 皇翔歡喜城</t>
+  </si>
+  <si>
+    <t>513 名軒快樂家</t>
+  </si>
+  <si>
+    <t>514 麗寶快樂家</t>
+  </si>
+  <si>
+    <t>總計</t>
+  </si>
+  <si>
+    <t>(空白)</t>
   </si>
 </sst>
 </file>
@@ -4595,7 +4776,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4633,6 +4814,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -4649,6 +4839,4647 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44717.366791319444" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="56" xr:uid="{473F2200-E745-354A-9F59-9FAA1012A14F}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:BQ57" sheet="工作表1"/>
+  </cacheSource>
+  <cacheFields count="69">
+    <cacheField name="No" numFmtId="176">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="101" maxValue="514"/>
+    </cacheField>
+    <cacheField name="區域" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="建案" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="N建案" numFmtId="0">
+      <sharedItems count="56">
+        <s v="101 和發大境"/>
+        <s v="102 鴻典"/>
+        <s v="103 樂捷市"/>
+        <s v="104 奇幻莊園"/>
+        <s v="105 樂田田"/>
+        <s v="106 玉子園"/>
+        <s v="107 台北國際村"/>
+        <s v="108 豐邑氧森"/>
+        <s v="201 富宇上城"/>
+        <s v="202 禾悅花園"/>
+        <s v="203 耀台北"/>
+        <s v="204 皇普MVP"/>
+        <s v="205 富宇敦峰"/>
+        <s v="206 玄泰V1"/>
+        <s v="207 和耀恆美"/>
+        <s v="301 允將大作"/>
+        <s v="302 欣時代"/>
+        <s v="303 新潤翡麗"/>
+        <s v="304 新潤鉑麗"/>
+        <s v="305 根津苑"/>
+        <s v="306 華悅城"/>
+        <s v="307 富宇悅峰"/>
+        <s v="308 合遠新天地"/>
+        <s v="309 友文化"/>
+        <s v="310 水悅青青"/>
+        <s v="311 文華天際"/>
+        <s v="312 君邑羅浮"/>
+        <s v="313 大亮時代A7"/>
+        <s v="314 大亮 泊"/>
+        <s v="401 竹城甲子園"/>
+        <s v="402 金捷市"/>
+        <s v="403 捷市達"/>
+        <s v="404 詠勝市中欣"/>
+        <s v="405 新A7"/>
+        <s v="406 富御捷境"/>
+        <s v="407 富宇哈佛苑"/>
+        <s v="408 頤昌豐岳"/>
+        <s v="409 新未來2"/>
+        <s v="410 新未來3"/>
+        <s v="411 和洲金剛"/>
+        <s v="412 君邑丘比特"/>
+        <s v="413 頤昌璞岳"/>
+        <s v="414 合謙學"/>
+        <s v="416 維特魯威"/>
+        <s v="417 頤昌澄岳"/>
+        <s v="418 玄泰T1"/>
+        <s v="501 新未來1"/>
+        <s v="502 富宇天匯"/>
+        <s v="503 竹城明治"/>
+        <s v="504 竹城宇治"/>
+        <s v="505 櫻花澍"/>
+        <s v="506 和煦隆陞"/>
+        <s v="511 遠雄文青"/>
+        <s v="512 皇翔歡喜城"/>
+        <s v="513 名軒快樂家"/>
+        <s v="514 麗寶快樂家"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Figure" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Link" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="實價2021" numFmtId="177">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="21.19" maxValue="36.78"/>
+    </cacheField>
+    <cacheField name="實價總平均或登錄筆數" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="21.34" maxValue="32.74"/>
+    </cacheField>
+    <cacheField name="最高實價" numFmtId="177">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="24.53" maxValue="48.58"/>
+    </cacheField>
+    <cacheField name="最低實價" numFmtId="177">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="11.84" maxValue="35.590000000000003"/>
+    </cacheField>
+    <cacheField name="每坪開價2020" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="2020每坪開價-最低" numFmtId="178">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="15" maxValue="39"/>
+    </cacheField>
+    <cacheField name="2020每坪開價-最高" numFmtId="178">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="15" maxValue="43"/>
+    </cacheField>
+    <cacheField name="每坪價-平均" numFmtId="178">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="15" maxValue="41"/>
+    </cacheField>
+    <cacheField name="2020價差" numFmtId="178">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="2.5"/>
+    </cacheField>
+    <cacheField name="每坪開價2022" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="每坪價2022-最低" numFmtId="178">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="15" maxValue="45"/>
+    </cacheField>
+    <cacheField name="每坪價2022-最高" numFmtId="178">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="15" maxValue="50"/>
+    </cacheField>
+    <cacheField name="2022價差" numFmtId="178">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="36"/>
+    </cacheField>
+    <cacheField name="每坪價2022-平均" numFmtId="178">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="47.5"/>
+    </cacheField>
+    <cacheField name="不變" numFmtId="178">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="FacebookName" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="FacebookLink" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="LineID" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="車位價格" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="車位價格-最低" numFmtId="179">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="115" maxValue="200"/>
+    </cacheField>
+    <cacheField name="車位價格-最高" numFmtId="179">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="169" maxValue="230"/>
+    </cacheField>
+    <cacheField name="貸款成數" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0.75" maxValue="0.8"/>
+    </cacheField>
+    <cacheField name="公開銷售" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="交屋時間" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="交屋年份" numFmtId="176">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2016" maxValue="2026" count="10">
+        <n v="2022"/>
+        <n v="2019"/>
+        <n v="2020"/>
+        <n v="2021"/>
+        <n v="2025"/>
+        <n v="2023"/>
+        <n v="2024"/>
+        <m/>
+        <n v="2026"/>
+        <n v="2016"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="交屋時程" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="交屋屋況" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="格局規劃" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Category1" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="建物形態" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="基地地址" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="接待會館" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="投資建設F" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="投資建設" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="建設公司" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="營造公司" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="企劃銷售" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="建案特色" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="公設比" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0.315" maxValue="0.34"/>
+    </cacheField>
+    <cacheField name="公設比例" numFmtId="10">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.315" maxValue="0.36799999999999999"/>
+    </cacheField>
+    <cacheField name="棟戶規劃" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="住家戶數" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="22" maxValue="1780"/>
+    </cacheField>
+    <cacheField name="商店戶數" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="31"/>
+    </cacheField>
+    <cacheField name="建蔽率" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0.2928" maxValue="0.63100000000000001"/>
+    </cacheField>
+    <cacheField name="建蔽比率" numFmtId="10">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.2928" maxValue="0.6502"/>
+    </cacheField>
+    <cacheField name="樓層規劃" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="樓層數" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="8" maxValue="31"/>
+    </cacheField>
+    <cacheField name="車位規劃" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="管理費用" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="車位配比" numFmtId="49">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="車位分配率" numFmtId="177">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.36" maxValue="1.17"/>
+    </cacheField>
+    <cacheField name="結構工程" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="基地面積" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="建築面積" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="332.5" maxValue="4720.8900000000003"/>
+    </cacheField>
+    <cacheField name="用途規劃" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="土地分區" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="物業公司" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="管委會" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="建造執照" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="建築設計" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="使用執照" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="行政里" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="56">
+  <r>
+    <n v="101"/>
+    <s v="1.樂善國小生活圈"/>
+    <s v="和發大境"/>
+    <x v="0"/>
+    <s v="fig/AiCity-939-和發大境.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=125726"/>
+    <n v="27.72"/>
+    <s v="179/292"/>
+    <n v="32.01"/>
+    <n v="24.3"/>
+    <s v="28~29 萬/坪"/>
+    <n v="28"/>
+    <n v="29"/>
+    <n v="28.5"/>
+    <n v="0.5"/>
+    <s v="34~36 萬/坪"/>
+    <n v="34"/>
+    <n v="36"/>
+    <n v="2"/>
+    <n v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="170~205萬"/>
+    <n v="170"/>
+    <n v="205"/>
+    <n v="0.8"/>
+    <s v="銷售中"/>
+    <s v="2022年下半年"/>
+    <x v="0"/>
+    <s v="2022Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(26~28坪) 、三房(39~40坪) 、四房(44坪) 、2+1房(33坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區長慶三街"/>
+    <s v="桃園市龜山區文化一路123號 "/>
+    <s v="和發建設股份有限公司"/>
+    <s v="和發建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="五十甲廣告股份有限公司"/>
+    <s v="近捷運、景觀宅、制震宅、近公園、重劃區、低首付"/>
+    <n v="0.33"/>
+    <n v="0.33"/>
+    <s v="3幢，8棟，280戶住家，12戶店面"/>
+    <n v="280"/>
+    <n v="12"/>
+    <n v="0.40899999999999997"/>
+    <n v="0.40899999999999997"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式318個"/>
+    <s v="待定"/>
+    <s v="1:1.09"/>
+    <n v="1.0900000000000001"/>
+    <s v="RC"/>
+    <s v="1586.57坪"/>
+    <n v="1586.57"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00546-01號"/>
+    <s v="拓璞聯合建築師事務所(聶玉璞)"/>
+    <s v="暫無"/>
+    <s v="長庚里"/>
+  </r>
+  <r>
+    <n v="102"/>
+    <s v="1.樂善國小生活圈"/>
+    <s v="鴻典"/>
+    <x v="1"/>
+    <s v="fig/AiCity-939-鴻典.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122584&amp;v=720"/>
+    <n v="24.35"/>
+    <n v="23.38"/>
+    <n v="26.49"/>
+    <n v="20.440000000000001"/>
+    <s v="26萬元/坪"/>
+    <n v="26"/>
+    <n v="26"/>
+    <n v="26"/>
+    <n v="0"/>
+    <s v="29萬元/坪"/>
+    <n v="29"/>
+    <n v="29"/>
+    <n v="0"/>
+    <n v="29"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="180~210萬"/>
+    <n v="180"/>
+    <n v="210"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2022年第一季"/>
+    <x v="0"/>
+    <s v="2022Q1"/>
+    <s v="標準配備"/>
+    <s v="二房(24-28坪)、三房(33-38坪)、4房(42坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區長慶三街"/>
+    <s v="桃園市龜山區長慶三街"/>
+    <s v="鴻築建設股份有限公司"/>
+    <s v="鴻築建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="商雋實業有限公司"/>
+    <s v="景觀宅、制震宅、近公園、重劃區、低首付"/>
+    <s v="32%"/>
+    <n v="0.32"/>
+    <s v="1幢，2棟，196戶住家，11戶店面"/>
+    <n v="196"/>
+    <n v="11"/>
+    <s v="39.8%"/>
+    <n v="0.39800000000000002"/>
+    <s v="地上15層，地下3層"/>
+    <n v="15"/>
+    <s v="平面式214個"/>
+    <s v="60元/坪/月"/>
+    <s v="1:1.03"/>
+    <n v="1.03"/>
+    <s v="RC"/>
+    <s v="1062.93坪"/>
+    <n v="1062.93"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="107桃市都建執照字第01412-01號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="103"/>
+    <s v="1.樂善國小生活圈"/>
+    <s v="樂捷市"/>
+    <x v="2"/>
+    <s v="fig/AiCity-939-樂捷市.jpeg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116751&amp;v=720"/>
+    <n v="24.46"/>
+    <n v="22.58"/>
+    <n v="31.05"/>
+    <n v="17.47"/>
+    <s v="26萬元/坪"/>
+    <n v="26"/>
+    <n v="26"/>
+    <n v="26"/>
+    <n v="0"/>
+    <s v="26萬元/坪"/>
+    <n v="26"/>
+    <n v="26"/>
+    <n v="0"/>
+    <n v="26"/>
+    <s v="Y"/>
+    <s v="樂捷市好鄰居"/>
+    <s v="https://www.facebook.com/groups/324107612343329"/>
+    <m/>
+    <s v="150~195萬"/>
+    <n v="150"/>
+    <n v="195"/>
+    <s v="85%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="1"/>
+    <s v="2019Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(26坪)、三房(38坪)、1+1房(25坪)、3+1房(44坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓/住商用"/>
+    <s v="桃園市龜山區長慶三街18號"/>
+    <s v="桃園市龜山區長慶三街18號1樓"/>
+    <s v="鴻築建設股份有限公司"/>
+    <s v="鴻築建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="商雋實業有限公司"/>
+    <s v="近捷運、明星學區、制震宅、近公園、重劃區"/>
+    <s v="31.5%"/>
+    <n v="0.315"/>
+    <s v="1幢，8棟，326戶住家，20戶店面"/>
+    <n v="326"/>
+    <n v="20"/>
+    <s v="49.56%"/>
+    <n v="0.49559999999999998"/>
+    <s v="地上15層，地下3層"/>
+    <n v="15"/>
+    <s v="平面式285個、機械式61個"/>
+    <s v="待定"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="1848.44坪"/>
+    <n v="1848.44"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="（106)桃市都建執照字第00372號等1個"/>
+    <s v="聶玉璞"/>
+    <s v="暫無"/>
+    <s v="長庚里"/>
+  </r>
+  <r>
+    <n v="104"/>
+    <s v="1.樂善國小生活圈"/>
+    <s v="奇幻莊園"/>
+    <x v="3"/>
+    <s v="fig/AiCity-939-奇幻莊園.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116476&amp;v=720"/>
+    <m/>
+    <n v="22.11"/>
+    <n v="27.38"/>
+    <n v="19.579999999999998"/>
+    <s v="24.5~25.5萬元/坪"/>
+    <n v="24.5"/>
+    <n v="25.5"/>
+    <n v="25"/>
+    <n v="0.5"/>
+    <s v="24.5~25.5萬元/坪"/>
+    <n v="24.5"/>
+    <n v="25.5"/>
+    <n v="1"/>
+    <n v="25"/>
+    <s v="Y"/>
+    <s v="龜山A7-奇幻莊園住戶"/>
+    <s v="https://www.facebook.com/groups/588376114975687"/>
+    <m/>
+    <s v="160~220萬"/>
+    <n v="160"/>
+    <n v="220"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="2"/>
+    <s v="2020Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(25~27坪)、三房(34-38坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區長慶二街"/>
+    <s v="桃園市龜山區長慶二街"/>
+    <s v="佳晟建設股份有限公司"/>
+    <s v="佳晟建設"/>
+    <s v="寶佳集團"/>
+    <s v="萬代營造有限公司"/>
+    <s v="商雋實業有限公司"/>
+    <s v="近捷運、近公園、重劃區"/>
+    <s v="32%"/>
+    <n v="0.32"/>
+    <s v="1幢，3棟，173戶住家，11戶店面"/>
+    <n v="173"/>
+    <n v="11"/>
+    <s v="48.26%"/>
+    <n v="0.48259999999999997"/>
+    <s v="地上13,14層，地下4層"/>
+    <n v="14"/>
+    <s v="平面式181個、機械式61個"/>
+    <s v="55元/坪/月"/>
+    <s v="1:0.98"/>
+    <n v="0.98"/>
+    <s v="RC"/>
+    <s v="954.46坪"/>
+    <n v="954.46"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="106桃市都建執照字第01160-01號"/>
+    <s v="林大俊建築師事務所"/>
+    <s v="暫無"/>
+    <s v="長庚里"/>
+  </r>
+  <r>
+    <n v="105"/>
+    <s v="1.樂善國小生活圈"/>
+    <s v="樂田田"/>
+    <x v="4"/>
+    <s v="fig/AiCity-939-樂甜甜.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121200&amp;v=720"/>
+    <n v="22.84"/>
+    <s v="203/199"/>
+    <n v="26.27"/>
+    <n v="19.62"/>
+    <s v="25~26 萬/坪"/>
+    <n v="25"/>
+    <n v="26"/>
+    <n v="25.5"/>
+    <n v="0.5"/>
+    <s v="25~26 萬/坪"/>
+    <n v="26"/>
+    <n v="26"/>
+    <n v="0"/>
+    <n v="26"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="190~230萬"/>
+    <n v="190"/>
+    <n v="230"/>
+    <n v="0.8"/>
+    <s v="銷售中"/>
+    <s v="2021年第三季度"/>
+    <x v="0"/>
+    <s v="2022Q1"/>
+    <s v="標準配備"/>
+    <s v="二房(23坪) 、2+1房(29坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區長慶二街與長慶三街 "/>
+    <s v="桃園市龜山區文化一路旁 "/>
+    <s v="佳晟建設股份有限公司"/>
+    <s v="佳晟建設"/>
+    <s v="寶佳集團"/>
+    <s v="萬代福營造有限公司"/>
+    <s v="群旺廣告有限公司"/>
+    <s v="景觀宅、重劃區"/>
+    <n v="0.32600000000000001"/>
+    <n v="0.32600000000000001"/>
+    <s v="2幢，4棟，187戶住家，12戶店面"/>
+    <n v="187"/>
+    <n v="12"/>
+    <n v="0.44269999999999998"/>
+    <n v="0.44269999999999998"/>
+    <s v="地上13、14層，地下4層"/>
+    <n v="14"/>
+    <s v="平面式173個"/>
+    <s v="55元/坪/月"/>
+    <s v="1:0.87"/>
+    <n v="0.87"/>
+    <s v="RC"/>
+    <s v="907.61坪"/>
+    <n v="907.61"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00290-01號"/>
+    <s v="林大俊建築師事務所"/>
+    <s v="暫無"/>
+    <s v="長庚里"/>
+  </r>
+  <r>
+    <n v="106"/>
+    <s v="1.樂善國小生活圈"/>
+    <s v="玉子園"/>
+    <x v="5"/>
+    <s v="fig/AiCity-939-玉子園.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=119531&amp;v=720"/>
+    <n v="21.64"/>
+    <n v="21.7"/>
+    <n v="24.53"/>
+    <n v="20.03"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="27"/>
+    <n v="1"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="2"/>
+    <n v="27"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="130~205萬"/>
+    <n v="130"/>
+    <n v="205"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年第四季"/>
+    <x v="3"/>
+    <s v="2021Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(24~27坪)、三房(36~43坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂捷段地號136, 140"/>
+    <s v="桃園市龜山區文化一路與華亞三路交口"/>
+    <s v="協勝建設股份有限公司"/>
+    <s v="協勝建設"/>
+    <s v="寶佳集團"/>
+    <s v="洛城營造有限公司"/>
+    <s v="漢乙廣告有限公司"/>
+    <s v="明星學區、景觀宅、低首付"/>
+    <s v="31~32%"/>
+    <n v="0.315"/>
+    <s v="5棟，186戶住家，7戶店面"/>
+    <n v="186"/>
+    <n v="7"/>
+    <s v="44.23%"/>
+    <n v="0.44230000000000003"/>
+    <s v="地上15層，地下3層"/>
+    <n v="15"/>
+    <s v="平面式178個、機械式14個"/>
+    <s v="待定"/>
+    <s v="1:0.99"/>
+    <n v="0.99"/>
+    <s v="RC"/>
+    <s v="1042.98坪"/>
+    <n v="1042.98"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜00880-01號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="長庚里"/>
+  </r>
+  <r>
+    <n v="107"/>
+    <s v="1.樂善國小生活圈"/>
+    <s v="台北國際村"/>
+    <x v="6"/>
+    <s v="fig/AiCity-939-台北國際村.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118714&amp;v=720"/>
+    <n v="22.83"/>
+    <n v="21.34"/>
+    <n v="25.94"/>
+    <n v="19.53"/>
+    <s v="25~26萬元/坪"/>
+    <n v="25"/>
+    <n v="26"/>
+    <n v="25.5"/>
+    <n v="0.5"/>
+    <s v="27~29 萬/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="2"/>
+    <n v="28"/>
+    <m/>
+    <s v="台北國際村住戶交流園區_林口A7"/>
+    <s v="https://www.facebook.com/groups/2397202740545114"/>
+    <m/>
+    <s v="160~195萬"/>
+    <n v="160"/>
+    <n v="195"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年第一季"/>
+    <x v="3"/>
+    <s v="2021Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(26~28坪)、三房(33~38坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂安街71號"/>
+    <s v="桃園市龜山區文化一路，文樂路交叉口"/>
+    <s v="和發建設股份有限公司"/>
+    <s v="和發建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="五十甲廣告股份有限公司"/>
+    <s v="近捷運、明星學區、制震宅、近公園、重劃區"/>
+    <s v="31~32%"/>
+    <n v="0.315"/>
+    <s v="4棟，198戶住家，8戶店面"/>
+    <n v="198"/>
+    <n v="8"/>
+    <s v="45.67%"/>
+    <n v="0.45669999999999999"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式206個"/>
+    <s v="待定"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="1054.47坪"/>
+    <n v="1054.47"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(107)桃市都建執照字第會龜01092-01號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="長庚里"/>
+  </r>
+  <r>
+    <n v="108"/>
+    <s v="1.樂善國小生活圈"/>
+    <s v="豐邑氧森"/>
+    <x v="7"/>
+    <s v="fig/AiCity-939-豐邑氧森.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=129338"/>
+    <n v="36.78"/>
+    <s v="12/328"/>
+    <n v="38.119999999999997"/>
+    <n v="35.590000000000003"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="41 萬/坪"/>
+    <n v="41"/>
+    <n v="41"/>
+    <m/>
+    <n v="41"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="200萬"/>
+    <n v="200"/>
+    <n v="200"/>
+    <m/>
+    <s v="銷售中"/>
+    <s v="2025年第四季度"/>
+    <x v="4"/>
+    <s v="2025Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(24~25坪) 、 三房(33~41坪) 、 2+1房(27~30坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住商用"/>
+    <s v=" 桃園市龜山區樂學路622巷"/>
+    <s v=" 桃園市龜山區樂學路622巷"/>
+    <s v="豐邑建設股份有限公司"/>
+    <s v="豐邑建設"/>
+    <s v="豐邑建設"/>
+    <s v="頌揚營造股份有限公司"/>
+    <s v="創意家行銷股份有限公司"/>
+    <m/>
+    <n v="0.33110000000000001"/>
+    <n v="0.33110000000000001"/>
+    <s v="1幢，8棟，320戶住家，8戶店面"/>
+    <n v="320"/>
+    <n v="8"/>
+    <n v="0.2928"/>
+    <n v="0.2928"/>
+    <s v="地上21層，地下4層"/>
+    <n v="21"/>
+    <s v="平面式374個"/>
+    <s v="待定"/>
+    <s v="1:1.14"/>
+    <n v="1.1399999999999999"/>
+    <s v="RC"/>
+    <s v="1761.89坪"/>
+    <n v="1761.89"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <m/>
+    <m/>
+    <s v="108桃市都建執照字第01289號"/>
+    <s v="王銘鴻建築師事務所"/>
+    <m/>
+    <s v="長庚里"/>
+  </r>
+  <r>
+    <n v="201"/>
+    <s v="2.郵政物流園區"/>
+    <s v="富宇上城"/>
+    <x v="8"/>
+    <s v="fig/AiCity-939-富宇上城.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121156&amp;v=720"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="30~35萬元/坪"/>
+    <n v="30"/>
+    <n v="35"/>
+    <n v="32.5"/>
+    <n v="2.5"/>
+    <s v="44~49 萬/坪"/>
+    <n v="44"/>
+    <n v="49"/>
+    <n v="5"/>
+    <n v="46.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="170~205萬"/>
+    <n v="170"/>
+    <n v="205"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2023年第一季"/>
+    <x v="4"/>
+    <s v="2025Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(24坪) 、三房(31~39坪) 、四房(45坪) 、2+1房(28坪) 、3+1房(41坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂捷段56地號"/>
+    <s v="桃園縣龜山鄉文化一路"/>
+    <s v="富宇建設股份有限公司"/>
+    <s v="富宇建設"/>
+    <s v="富宇建設"/>
+    <s v="盛傑營造有限公司"/>
+    <s v="華昱廣告有限公司"/>
+    <s v="華昱廣告"/>
+    <s v="33.5%"/>
+    <n v="0.33500000000000002"/>
+    <s v="4幢，6棟，832戶住家"/>
+    <n v="832"/>
+    <n v="0"/>
+    <s v="31.07%"/>
+    <n v="0.31069999999999998"/>
+    <s v="地上24層，地下4層"/>
+    <n v="24"/>
+    <s v="平面式933個"/>
+    <s v="75元/坪/月"/>
+    <s v="1:1.12"/>
+    <n v="1.1200000000000001"/>
+    <s v="RC"/>
+    <s v="4046.9坪"/>
+    <n v="4046.9"/>
+    <s v="住商用"/>
+    <s v="產業專用區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(107)桃市都建執照字第會龜00519-01號等1個"/>
+    <s v="吳六合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="202"/>
+    <s v="2.郵政物流園區"/>
+    <s v="禾悅花園"/>
+    <x v="9"/>
+    <s v="fig/AiCity-939-禾悅花園.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122734&amp;v=720"/>
+    <n v="29.88"/>
+    <s v="929/1044"/>
+    <n v="37.450000000000003"/>
+    <n v="21.36"/>
+    <s v="28~29萬元/坪"/>
+    <n v="28"/>
+    <n v="29"/>
+    <n v="28.5"/>
+    <n v="0.5"/>
+    <s v="35~37 萬/坪"/>
+    <n v="35"/>
+    <n v="37"/>
+    <n v="2"/>
+    <n v="36"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="130~200萬"/>
+    <n v="130"/>
+    <n v="200"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2024年第二季"/>
+    <x v="4"/>
+    <s v="2025Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(22~23坪) 、三房(30~37坪) 、四房(46~47坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文禾路、文達路及樂學路口"/>
+    <s v="桃園市龜山區文桃路及文茂路口"/>
+    <s v="禾聯股份有限公司"/>
+    <s v="禾聯建築"/>
+    <s v="禾聯建築"/>
+    <s v="禾華營造股份有限公司(甲級)"/>
+    <s v="海悅國際開發股份有限公司司"/>
+    <s v="明星學區、景觀宅、近公園、低首付"/>
+    <s v="33.5%"/>
+    <n v="0.33500000000000002"/>
+    <s v="1幢，13棟，1044戶住家"/>
+    <n v="1044"/>
+    <n v="0"/>
+    <s v="52.94%"/>
+    <n v="0.52939999999999998"/>
+    <s v="地上14~15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式1068個"/>
+    <s v="65元/坪/月"/>
+    <s v="1:1.02"/>
+    <n v="1.02"/>
+    <s v="RC"/>
+    <s v="4720.89坪"/>
+    <n v="4720.8900000000003"/>
+    <s v="住商用"/>
+    <s v="產業專用區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="109桃市都建執照字第00083號等1個"/>
+    <s v="廖錦盈建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="203"/>
+    <s v="2.郵政物流園區"/>
+    <s v="耀台北"/>
+    <x v="10"/>
+    <s v="fig/AiCity-939-耀台北.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118336&amp;v=720"/>
+    <n v="24.43"/>
+    <n v="22.23"/>
+    <n v="25.36"/>
+    <n v="19.66"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="27"/>
+    <n v="1"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="2"/>
+    <n v="27"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="170~195萬"/>
+    <n v="170"/>
+    <n v="195"/>
+    <s v="85%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="2"/>
+    <s v="2020Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(26-29坪)、三房(39~40坪)、4房(44坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂捷段地號 184"/>
+    <s v="桃園市龜山區文化一路103號"/>
+    <s v="和耀建設股份有限公司"/>
+    <s v="和耀建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="漢乙廣告有限公司"/>
+    <s v="近捷運、明星學區、景觀宅、近公園、重劃區、低首付"/>
+    <s v="31.5%"/>
+    <n v="0.315"/>
+    <s v="5棟，199戶住家，2戶店面"/>
+    <n v="199"/>
+    <n v="2"/>
+    <s v="46.14%"/>
+    <n v="0.46139999999999998"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式139個、機械式65個"/>
+    <s v="待定"/>
+    <s v="1:1.01"/>
+    <n v="1.01"/>
+    <s v="RC"/>
+    <s v="909.91坪"/>
+    <n v="909.91"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(107)桃市都建執照字第會龜00614號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="204"/>
+    <s v="2.郵政物流園區"/>
+    <s v="皇普MVP"/>
+    <x v="11"/>
+    <s v="fig/AiCity-939-皇普MVP.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118186"/>
+    <n v="24.17"/>
+    <s v="205/321"/>
+    <n v="26.76"/>
+    <n v="21.03"/>
+    <s v="25~26萬元/坪"/>
+    <n v="25"/>
+    <n v="26"/>
+    <n v="25.5"/>
+    <n v="0.5"/>
+    <s v="27~28 萬/坪"/>
+    <n v="27"/>
+    <n v="28"/>
+    <n v="1"/>
+    <n v="27.5"/>
+    <m/>
+    <s v="A7皇普MVP屋主交流團"/>
+    <s v="https://www.facebook.com/groups/800873736965340"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8"/>
+    <s v="銷售中"/>
+    <s v="2021年10月"/>
+    <x v="3"/>
+    <s v="2021Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(26~29坪) 、三房(37~40坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化一路"/>
+    <s v="桃園市龜山區文化一路73號對面 "/>
+    <s v="皇普建設股份有限公司"/>
+    <s v="皇普建設"/>
+    <s v="寶佳集團"/>
+    <s v="安興營造有限公司"/>
+    <s v="新理想廣告"/>
+    <s v="近捷運、明星學區、重劃區、低首付"/>
+    <n v="0.31859999999999999"/>
+    <n v="0.31859999999999999"/>
+    <s v="6棟，308戶住家，13戶店面"/>
+    <n v="308"/>
+    <n v="13"/>
+    <n v="0.47989999999999999"/>
+    <n v="0.47989999999999999"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式276個、機械式45個"/>
+    <s v="50元/坪/月"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="1390.39坪"/>
+    <n v="1390.39"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(107)桃市都建執照字第會龜01075號"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="205"/>
+    <s v="2.郵政物流園區"/>
+    <s v="富宇敦峰"/>
+    <x v="12"/>
+    <s v="fig/AiCity-939-富宇敦峰.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116430&amp;v=720"/>
+    <n v="29.71"/>
+    <n v="25.55"/>
+    <n v="33.47"/>
+    <n v="22.21"/>
+    <s v="30~32萬元/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <n v="31"/>
+    <n v="1"/>
+    <s v="38~42 萬/坪"/>
+    <n v="38"/>
+    <n v="42"/>
+    <n v="4"/>
+    <n v="40"/>
+    <m/>
+    <s v="富宇敦峰住戶社團"/>
+    <s v="https://www.facebook.com/groups/124542338433380"/>
+    <m/>
+    <s v="180~195萬"/>
+    <n v="180"/>
+    <n v="195"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="2"/>
+    <s v="2020Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(29坪) 、三房(38坪) 、四房(49坪) 、2+1房(32坪) 、3+1房(43坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂善國小旁"/>
+    <s v="桃園市龜山區文化一路.華亞三路口"/>
+    <s v="富宇建設股份有限公司"/>
+    <s v="富宇建設"/>
+    <s v="富宇建設"/>
+    <s v="盛傑營造"/>
+    <s v="華威廣告"/>
+    <s v="明星學區、景觀宅、近公園、重劃區、低首付"/>
+    <s v="33.35%"/>
+    <n v="0.33350000000000002"/>
+    <s v="8棟，441戶住家，7戶店面"/>
+    <n v="441"/>
+    <n v="7"/>
+    <s v="43.92%"/>
+    <n v="0.43919999999999998"/>
+    <s v="地上15層，地下3層"/>
+    <n v="15"/>
+    <s v="平面式465個"/>
+    <s v="65元/坪/月"/>
+    <s v="1:1.04"/>
+    <n v="1.04"/>
+    <s v="RC"/>
+    <s v="2727.34坪"/>
+    <n v="2727.34"/>
+    <s v="住商用"/>
+    <s v="第四種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="107桃市都建執照0680號等1個"/>
+    <s v="吳六合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="206"/>
+    <s v="2.郵政物流園區"/>
+    <s v="玄泰V1"/>
+    <x v="13"/>
+    <s v="fig/AiCity-939-玄泰V1.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=120098&amp;v=720"/>
+    <m/>
+    <n v="22.46"/>
+    <n v="28.11"/>
+    <n v="19.04"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="28"/>
+    <n v="1"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="2"/>
+    <n v="28"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="155~195萬"/>
+    <n v="155"/>
+    <n v="195"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2022年下半年"/>
+    <x v="5"/>
+    <s v="2023Q1"/>
+    <s v="標準配備"/>
+    <s v="二房(21~28坪)、三房(30~46坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化一路&amp;樂安街路口"/>
+    <s v="桃園市龜山區文化一路&amp;文樂路口"/>
+    <s v="允泰開發有限公司"/>
+    <s v="允泰開發"/>
+    <s v="玄泰建設"/>
+    <s v="益盛營造"/>
+    <s v="天湛廣告"/>
+    <s v="近捷運、重劃區"/>
+    <s v="31.9%"/>
+    <n v="0.31900000000000001"/>
+    <s v="2棟，138戶住家，8戶店面，125戶一般事務所"/>
+    <n v="138"/>
+    <n v="8"/>
+    <s v="60.16%"/>
+    <n v="0.60160000000000002"/>
+    <s v="地上24層，地下5層"/>
+    <n v="24"/>
+    <s v="平面式284個"/>
+    <s v="待定"/>
+    <s v="1:1.05"/>
+    <n v="1.05"/>
+    <s v="RC"/>
+    <s v="911.52坪"/>
+    <n v="911.52"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(108)桃市都建執照字第會龜00216號等1個"/>
+    <s v="新森峰建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="207"/>
+    <s v="2.郵政物流園區"/>
+    <s v="和耀恆美"/>
+    <x v="14"/>
+    <s v="fig/AiCity-939-和耀恆美.jpeg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122650&amp;v=720"/>
+    <n v="25.24"/>
+    <s v="134/291"/>
+    <n v="30.14"/>
+    <n v="21.86"/>
+    <s v="28~33 萬/坪"/>
+    <n v="28"/>
+    <n v="33"/>
+    <n v="30.5"/>
+    <n v="2.5"/>
+    <s v="35~40 萬/坪"/>
+    <n v="35"/>
+    <n v="40"/>
+    <n v="5"/>
+    <n v="37.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="待訂"/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2022年第二季度"/>
+    <x v="0"/>
+    <s v="2022Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(27~29坪) 、 三房(36~48坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂捷段172地號"/>
+    <s v="桃園市龜山區文化一路&amp;樂學路口 "/>
+    <s v="和耀建設股份有限公司"/>
+    <s v="和耀建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="漢乙廣告事業有限公司"/>
+    <s v="和耀恆美基地緊鄰樂善科技園區，是北台灣新科技聚落，未來將可活絡地方經濟，本案位處第一排優勢。主打公園景觀，2000坪公園綠地以及自然保護區第一排，享有無限景觀視野棟距，開窗即見綠意美景。"/>
+    <s v="32~32.5%"/>
+    <n v="0.32250000000000001"/>
+    <s v="1幢，7棟，280戶住家，11戶店面"/>
+    <n v="280"/>
+    <n v="11"/>
+    <n v="0.4743"/>
+    <n v="0.4743"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式236個、機械式59個"/>
+    <s v="待定"/>
+    <s v="1:1.01"/>
+    <n v="1.01"/>
+    <s v="RC"/>
+    <s v="1309.14坪"/>
+    <n v="1309.1400000000001"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <m/>
+    <s v="暫無"/>
+    <s v="107桃市都建執照字第00925-01號"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="301"/>
+    <s v="3.中心商業區"/>
+    <s v="允將大作"/>
+    <x v="15"/>
+    <s v="fig/AiCity-939-允將大作.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=124450"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="35~38萬元/坪"/>
+    <n v="35"/>
+    <n v="38"/>
+    <n v="36.5"/>
+    <n v="1.5"/>
+    <s v="38~43 萬/坪"/>
+    <n v="38"/>
+    <n v="43"/>
+    <n v="5"/>
+    <n v="40.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="140~210萬"/>
+    <n v="140"/>
+    <n v="210"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2028年第二季度"/>
+    <x v="4"/>
+    <s v="202５Q2"/>
+    <s v="標準配備"/>
+    <s v="一房(18坪) 、二房(22~27坪) 、三房(31~42坪) 、店面(58~160坪) 、辦公室(18~42坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化一路、樂善三路口 "/>
+    <s v="桃園市龜山區文化一路568號 "/>
+    <s v="允將建設股份有限公司"/>
+    <s v="允將建設"/>
+    <s v="允將建設"/>
+    <s v="東霙營造股份有限公司"/>
+    <s v="時詣廣告股份有限公司"/>
+    <s v="近捷運、明星學區、景觀宅、制震宅、近公園、重劃區、低首付"/>
+    <n v="0.33800000000000002"/>
+    <n v="0.33800000000000002"/>
+    <s v="1幢，7棟，530戶住家，5戶店面，20戶事務所，1戶管委會空間"/>
+    <n v="530"/>
+    <n v="5"/>
+    <n v="0.45529999999999998"/>
+    <n v="0.45529999999999998"/>
+    <s v="地上31層，地下6層"/>
+    <n v="31"/>
+    <s v="平面式563個"/>
+    <s v="80元/坪/月"/>
+    <s v="1:1.01"/>
+    <n v="1.01"/>
+    <s v="RC"/>
+    <s v="1554.48坪"/>
+    <n v="1554.48"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="106桃市都建執照字第00391-01號"/>
+    <s v="王銘鴻建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="302"/>
+    <s v="3.中心商業區"/>
+    <s v="欣時代"/>
+    <x v="16"/>
+    <s v="fig/AiCity-939-欣時代.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118905"/>
+    <m/>
+    <s v="154/258"/>
+    <n v="28.96"/>
+    <n v="19.2"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="28"/>
+    <n v="1"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="2"/>
+    <n v="28"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="170~205萬"/>
+    <n v="170"/>
+    <n v="205"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2023年下半年"/>
+    <x v="5"/>
+    <s v="2023Q4"/>
+    <s v="標準配備"/>
+    <s v="三房(31~35坪) 、2+1房(26~29坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化一路.華亞三路交叉口"/>
+    <s v="桃園市龜山區文化一路、文桃路口"/>
+    <s v="欣巴巴事業股份有限公司"/>
+    <s v="欣巴巴"/>
+    <s v="欣巴巴"/>
+    <s v="巴森營造股份有限公司"/>
+    <s v="新高創團隊，寰宇動力廣告有限公司"/>
+    <s v="近捷運、景觀宅、制震宅、近公園、重劃區、創意空間、低首付"/>
+    <s v="33.5%"/>
+    <n v="0.33500000000000002"/>
+    <s v="5棟，235戶住家，4戶店面，19戶一般事務所"/>
+    <n v="235"/>
+    <n v="4"/>
+    <s v="57.49%"/>
+    <n v="0.57489999999999997"/>
+    <s v="地上30層，地下6層"/>
+    <n v="30"/>
+    <s v="平面式235個"/>
+    <s v="待定"/>
+    <s v="1:0.91"/>
+    <n v="0.91"/>
+    <s v="RC"/>
+    <s v="713.17坪"/>
+    <n v="713.17"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜00288-02號等1個"/>
+    <s v="卓玲建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="303"/>
+    <s v="3.中心商業區"/>
+    <s v="新潤翡麗"/>
+    <x v="17"/>
+    <s v="fig/AiCity-939-新潤翡麗.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=117434&amp;v=720"/>
+    <n v="26.84"/>
+    <s v="435/450"/>
+    <n v="34.33"/>
+    <n v="17.09"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="27"/>
+    <n v="1"/>
+    <s v="33~36 萬/坪"/>
+    <n v="33"/>
+    <n v="36"/>
+    <n v="3"/>
+    <n v="34.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="160~190萬"/>
+    <n v="160"/>
+    <n v="190"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年第四季"/>
+    <x v="3"/>
+    <s v="2021Q4"/>
+    <s v="標準配備"/>
+    <s v="一房(15~17坪) 、二房(22坪) 、三房(26~31坪) 、2+1房(24坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化一路與華亞三路"/>
+    <s v="桃園市龜山區文化一路與華亞二路口"/>
+    <s v="新潤建設機構"/>
+    <s v="新潤建設"/>
+    <s v="新潤建設"/>
+    <s v="揚潤營造有限公司"/>
+    <s v="華磐國際開發股份有限公司"/>
+    <s v="近捷運、明星學區、景觀宅、重劃區、低首付"/>
+    <s v="33.5~34.5%"/>
+    <n v="0.33750000000000002"/>
+    <s v="1幢，2棟，420戶住家，20戶店面，11戶一般事務所"/>
+    <n v="420"/>
+    <n v="20"/>
+    <s v="65.02%"/>
+    <n v="0.6502"/>
+    <s v="地上24層，地下5層"/>
+    <n v="24"/>
+    <s v="平面式330個"/>
+    <s v="待定"/>
+    <s v="1:0.73"/>
+    <n v="0.73"/>
+    <s v="RC"/>
+    <s v="1083.97坪"/>
+    <n v="1083.97"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜00984-01號等1個"/>
+    <s v="蕭家福聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="304"/>
+    <s v="3.中心商業區"/>
+    <s v="新潤鉑麗"/>
+    <x v="18"/>
+    <s v="fig/AiCity-939-新潤鉑麗.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=119614"/>
+    <n v="26.4"/>
+    <n v="24.52"/>
+    <n v="29.11"/>
+    <n v="22.34"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="28"/>
+    <n v="1"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="2"/>
+    <n v="28"/>
+    <s v="Y"/>
+    <s v="新潤翡麗住戶天地"/>
+    <s v="https://www.facebook.com/groups/321511928734593"/>
+    <m/>
+    <s v="165~190萬"/>
+    <n v="165"/>
+    <n v="190"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="2"/>
+    <s v="2020Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(20坪) 、三房(27~35坪) 、2+1房(24坪) 、3+1房(36坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區華亞三路39巷2號 "/>
+    <s v="桃園市龜山區華亞三路39巷2號 "/>
+    <s v="新潤興業股份有限公司"/>
+    <s v="新潤興業"/>
+    <s v="新潤建設"/>
+    <s v="國原營造股份有限公司"/>
+    <s v="華麟廣告"/>
+    <s v="近捷運、明星學區、景觀宅、重劃區"/>
+    <n v="0.33500000000000002"/>
+    <n v="0.33500000000000002"/>
+    <s v="2幢，3棟，266戶住家，13戶店面"/>
+    <n v="266"/>
+    <n v="13"/>
+    <n v="0.59850000000000003"/>
+    <n v="0.59850000000000003"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式243個"/>
+    <s v="80元/坪/月"/>
+    <s v="1:0.87"/>
+    <n v="0.87"/>
+    <s v="RC"/>
+    <s v="1137.47坪"/>
+    <n v="1137.47"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="107桃市都建執照字第龜01089-01號"/>
+    <s v="蕭家福聯合建築師事務所"/>
+    <s v="109桃市都施使字第00666號"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="305"/>
+    <s v="3.中心商業區"/>
+    <s v="根津苑"/>
+    <x v="19"/>
+    <s v="fig/AiCity-939-根津苑.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=118143&amp;v=720"/>
+    <n v="23.36"/>
+    <n v="21.94"/>
+    <n v="28.07"/>
+    <n v="19.899999999999999"/>
+    <s v="24~26萬元/坪"/>
+    <n v="24"/>
+    <n v="26"/>
+    <n v="25"/>
+    <n v="1"/>
+    <s v="26~28 萬/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="2"/>
+    <n v="27"/>
+    <m/>
+    <s v="根津苑"/>
+    <s v="https://www.facebook.com/%E6%A0%B9%E6%B4%A5%E8%8B%91-102597158541363"/>
+    <m/>
+    <s v="160~190萬"/>
+    <n v="160"/>
+    <n v="190"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="2"/>
+    <s v="2020Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(25~28坪)、三房(36~40坪)、4房(49坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂善三路"/>
+    <s v="桃園市龜山區文化一路與華亜三路交口"/>
+    <s v="鴻承建設股份有限公司"/>
+    <s v="鴻承建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="永捷廣告有限公司"/>
+    <s v="近捷運、明星學區、制震宅、近公園、重劃區"/>
+    <s v="32%"/>
+    <n v="0.32"/>
+    <s v="4棟，225戶住家，3戶店面"/>
+    <n v="225"/>
+    <n v="3"/>
+    <s v="50.54%"/>
+    <n v="0.50539999999999996"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式228個"/>
+    <s v="待定"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="1848.44坪"/>
+    <n v="1848.44"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(107)桃市都建執照字第會龜00667號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="306"/>
+    <s v="3.中心商業區"/>
+    <s v="華悅城"/>
+    <x v="20"/>
+    <s v="fig/AiCity-939-華悅城.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=120741"/>
+    <m/>
+    <n v="25.61"/>
+    <n v="29.69"/>
+    <n v="22.7"/>
+    <s v="26~30萬元/坪"/>
+    <n v="26"/>
+    <n v="30"/>
+    <n v="28"/>
+    <n v="2"/>
+    <s v="26~30萬元/坪"/>
+    <n v="26"/>
+    <n v="30"/>
+    <n v="4"/>
+    <n v="28"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="150~195萬"/>
+    <n v="150"/>
+    <n v="195"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年下半年"/>
+    <x v="0"/>
+    <s v="2022Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(23坪) 、三房(32坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂善二路、樂善三路口"/>
+    <s v="桃園市龜山區文化一路"/>
+    <s v="興富發建設股份有限公司"/>
+    <s v="興富發建設"/>
+    <s v="興富發建設"/>
+    <s v="齊裕營造股份有限公司"/>
+    <s v="愛山林建設開發(股)公司"/>
+    <s v="近捷運、明星學區、景觀宅、近公園、重劃區、低首付"/>
+    <n v="0.34"/>
+    <n v="0.34"/>
+    <s v="3棟，776戶住家，8戶店面"/>
+    <n v="776"/>
+    <n v="8"/>
+    <n v="0.44359999999999999"/>
+    <n v="0.44359999999999999"/>
+    <s v="地上18層，地下4層"/>
+    <n v="18"/>
+    <s v="平面式590個、機械式119個"/>
+    <s v="待定"/>
+    <s v="1:0.9"/>
+    <n v="0.9"/>
+    <s v="RC"/>
+    <s v="2751.33坪"/>
+    <n v="2751.33"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(108)桃市都建執照字第會龜00410-01號"/>
+    <s v="廖蓮輝建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="307"/>
+    <s v="3.中心商業區"/>
+    <s v="富宇悅峰"/>
+    <x v="21"/>
+    <s v="fig/AiCity-939-富宇悅峰.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=119483&amp;v=720"/>
+    <n v="24.96"/>
+    <n v="25.01"/>
+    <n v="27.55"/>
+    <n v="23.49"/>
+    <s v="28~32萬元/坪"/>
+    <n v="28"/>
+    <n v="32"/>
+    <n v="30"/>
+    <n v="2"/>
+    <s v="34~36 萬/坪"/>
+    <n v="34"/>
+    <n v="36"/>
+    <n v="2"/>
+    <n v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="175~195萬"/>
+    <n v="175"/>
+    <n v="195"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2022年第一季"/>
+    <x v="0"/>
+    <s v="2022Q1"/>
+    <s v="標準配備"/>
+    <s v="二房(27~31坪) 、三房(27~31坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住家用"/>
+    <s v="桃園市龜山區善捷段地號 209"/>
+    <s v="桃園市龜山區文化一路與文桃路口"/>
+    <s v="富宇建設股份有限公司"/>
+    <s v="富宇建設"/>
+    <s v="富宇建設"/>
+    <s v="盛傑營造有限公司"/>
+    <s v="華威廣告有限公司"/>
+    <s v="近捷運、明星學區、景觀宅、近公園、重劃區、低首付"/>
+    <s v="33.5~40%"/>
+    <n v="0.36799999999999999"/>
+    <s v="5棟，264戶住家"/>
+    <n v="264"/>
+    <n v="0"/>
+    <s v="40.21%"/>
+    <n v="0.40210000000000001"/>
+    <s v="地上14層，地下4層"/>
+    <n v="14"/>
+    <s v="平面式227個"/>
+    <s v="70元/坪/月"/>
+    <s v="1:0.86"/>
+    <n v="0.86"/>
+    <s v="RC"/>
+    <s v="1266.01坪"/>
+    <n v="1266.01"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(108)桃市都建執照字第會龜00334號等1個"/>
+    <s v="徐瑞燦建築師事務所"/>
+    <s v="暫無"/>
+    <s v="文化里"/>
+  </r>
+  <r>
+    <n v="308"/>
+    <s v="3.中心商業區"/>
+    <s v="合遠新天地"/>
+    <x v="22"/>
+    <s v="fig/AiCity-939-合遠新天地.jpeg"/>
+    <m/>
+    <m/>
+    <n v="21.94"/>
+    <n v="25.21"/>
+    <n v="19.66"/>
+    <s v="24~26萬元/坪"/>
+    <n v="24"/>
+    <n v="26"/>
+    <n v="25"/>
+    <n v="1"/>
+    <s v="24~26萬元/坪"/>
+    <n v="24"/>
+    <n v="26"/>
+    <n v="2"/>
+    <n v="25"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="165~185萬"/>
+    <n v="165"/>
+    <n v="185"/>
+    <s v="80%"/>
+    <s v="已完銷"/>
+    <s v="隨時交屋"/>
+    <x v="1"/>
+    <s v="2019Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(27~28坪)、三房(36~43坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區華亞三路"/>
+    <s v="桃園市龜山區華亞三路"/>
+    <s v="合遠建設股份有限公司"/>
+    <s v="合遠建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="盛馨廣告有限公司"/>
+    <s v="近捷運、近公園、重劃區"/>
+    <s v="31~32%"/>
+    <n v="0.315"/>
+    <s v="2棟，112戶住家，4戶店面"/>
+    <n v="112"/>
+    <n v="4"/>
+    <s v="33.97%"/>
+    <n v="0.3397"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式104個、機械式14個"/>
+    <s v="待定"/>
+    <s v="1:1.02"/>
+    <n v="1.02"/>
+    <s v="RC"/>
+    <s v="642.92坪"/>
+    <n v="642.91999999999996"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜01161-01號等1個"/>
+    <s v="閤康聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="文化里"/>
+  </r>
+  <r>
+    <n v="309"/>
+    <s v="3.中心商業區"/>
+    <s v="友文化"/>
+    <x v="23"/>
+    <s v="fig/AiCity-939-友文化.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/info?hid=121155"/>
+    <n v="23.59"/>
+    <n v="22.72"/>
+    <n v="30.38"/>
+    <n v="20"/>
+    <s v="30~31萬元/坪"/>
+    <n v="30"/>
+    <n v="31"/>
+    <n v="30.5"/>
+    <n v="0.5"/>
+    <s v="28萬元/坪"/>
+    <n v="28"/>
+    <n v="28"/>
+    <n v="0"/>
+    <n v="28"/>
+    <m/>
+    <s v="友文化"/>
+    <s v="https://www.facebook.com/groups/710305099774047"/>
+    <m/>
+    <s v="195~215萬"/>
+    <n v="195"/>
+    <n v="215"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年第三季度"/>
+    <x v="3"/>
+    <s v="2021Q3"/>
+    <s v="標準配備"/>
+    <s v="二房(26~27坪) 、三房(37~42坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化二路、華亞三路口 "/>
+    <s v="桃園市龜山區華亞三路195號 "/>
+    <s v="合遠建設股份有限公司"/>
+    <s v="合遠建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="新高智廣告"/>
+    <s v="近捷運、景觀宅、近公園、重劃區、低首付"/>
+    <n v="0.32"/>
+    <n v="0.32"/>
+    <s v="3幢，7棟，305戶住家"/>
+    <n v="305"/>
+    <n v="0"/>
+    <n v="0.44209999999999999"/>
+    <n v="0.44209999999999999"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式279個、機械式26個"/>
+    <s v="50元/坪/月"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="1426.7坪"/>
+    <n v="1426.7"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(108)桃市都建執照字第會龜00050號"/>
+    <s v="蔡智勸建築師事務所"/>
+    <s v="暫無"/>
+    <s v="文化里"/>
+  </r>
+  <r>
+    <n v="310"/>
+    <s v="3.中心商業區"/>
+    <s v="水悅青青"/>
+    <x v="24"/>
+    <s v="fig/AiCity-939-水悅青青.webp"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=125625"/>
+    <n v="24.76"/>
+    <s v="104/211"/>
+    <n v="29.05"/>
+    <n v="21.81"/>
+    <s v="29~31 萬/坪"/>
+    <n v="29"/>
+    <n v="31"/>
+    <n v="30"/>
+    <n v="1"/>
+    <s v="34~39 萬/坪"/>
+    <n v="34"/>
+    <n v="39"/>
+    <n v="5"/>
+    <n v="36.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="190~210萬"/>
+    <n v="190"/>
+    <n v="210"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年10月"/>
+    <x v="3"/>
+    <s v="2021Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(25~28坪) 、 三房(38坪) 、 2+1房(34坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區善捷段28地號"/>
+    <s v="桃園市龜山區文化一路88-2號"/>
+    <s v="鴻承建設股份有限公司"/>
+    <s v="鴻承建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="永捷廣告"/>
+    <s v="水悅青青公園第一排職人施工 EPDM防水材 浴室止水墩公園 湖景 學區 捷運A8生活圈 華亞特區名宅聚落"/>
+    <n v="0.32"/>
+    <n v="0.32"/>
+    <s v="1幢，3棟，204戶住家，7戶店面"/>
+    <n v="204"/>
+    <n v="7"/>
+    <n v="0.55610000000000004"/>
+    <n v="0.55610000000000004"/>
+    <s v="地上13、14層，地下5層"/>
+    <n v="14"/>
+    <s v="平面式211個"/>
+    <s v="待定"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="910.52坪"/>
+    <n v="910.52"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <m/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00167號"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="311"/>
+    <s v="3.中心商業區"/>
+    <s v="文華天際"/>
+    <x v="25"/>
+    <s v="fig/AiCity-939-文華天際.png"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=127139"/>
+    <n v="25.71"/>
+    <s v="634/486"/>
+    <n v="31.03"/>
+    <n v="23.19"/>
+    <s v="27 萬/坪 "/>
+    <n v="27"/>
+    <n v="27"/>
+    <n v="27"/>
+    <n v="0"/>
+    <s v="32~34 萬/坪"/>
+    <n v="32"/>
+    <n v="34"/>
+    <n v="2"/>
+    <n v="33"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="115~217萬"/>
+    <n v="115"/>
+    <n v="217"/>
+    <s v="80%"/>
+    <s v="尚未開賣"/>
+    <s v="2024年第二季度"/>
+    <x v="6"/>
+    <s v="2024Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(24~28坪) 、 三房(29~36坪) 、 3+1房(41坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化二路、華亞三路口"/>
+    <s v="桃園市龜山區文桃路、樂善一路口"/>
+    <s v="合遠建設股份有限公司"/>
+    <s v="合遠建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="新誠家廣告有限公司"/>
+    <s v="Check in奢華的完美規劃超高22層A7新視野，點亮城市天際線全台最美科學園區首排規劃極品15項全齡公設，構築家人相聚無憂假期夏季日光戶外泳池、置身城市星級旅店盡興探索都會享樂品味不只是居宅，傲視全A7實現精彩休旅生活體驗陽光泳池雙園景25-41坪"/>
+    <n v="0.32500000000000001"/>
+    <n v="0.33"/>
+    <s v="1幢，2棟，478戶住家，8戶店面"/>
+    <n v="478"/>
+    <n v="8"/>
+    <n v="0.3347"/>
+    <n v="0.3347"/>
+    <s v="地上22層，地下4層"/>
+    <n v="22"/>
+    <s v="平面式440個、機械式46個"/>
+    <s v="待定"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="1998.07坪"/>
+    <n v="1998.07"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <m/>
+    <s v="暫無"/>
+    <s v="109桃市都建執照字第00376-01號"/>
+    <s v="蔡智勸建築師事務所"/>
+    <s v="暫無"/>
+    <s v="文化里"/>
+  </r>
+  <r>
+    <n v="312"/>
+    <s v="3.中心商業區"/>
+    <s v="君邑羅浮"/>
+    <x v="26"/>
+    <s v="fig/AiCity-939-君邑羅浮.jpg"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="7"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="313"/>
+    <s v="3.中心商業區"/>
+    <s v="大亮時代A7"/>
+    <x v="27"/>
+    <s v="fig/AiCity-939-大亮時代A7.jpeg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=125949"/>
+    <n v="29.4"/>
+    <s v="129/135"/>
+    <n v="34.24"/>
+    <n v="27.17"/>
+    <s v="35~36 萬/坪"/>
+    <n v="35"/>
+    <n v="36"/>
+    <n v="35.5"/>
+    <n v="0.5"/>
+    <s v="35~36 萬/坪"/>
+    <n v="35"/>
+    <n v="36"/>
+    <n v="1"/>
+    <n v="35.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="148~169萬"/>
+    <n v="148"/>
+    <n v="169"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2023年第四季度"/>
+    <x v="5"/>
+    <s v="2023Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(15.8~23.2坪) 、 三房(26.2坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住家用"/>
+    <s v="桃園市龜山區善捷段166地號"/>
+    <s v="桃園市龜山區文化一路、樂善二路口"/>
+    <s v="大亮建築股份有限公司"/>
+    <s v="大亮建築"/>
+    <s v="大亮建築"/>
+    <s v="大亮營造股份有限公司"/>
+    <s v="大亮建築股份有限公司"/>
+    <s v="周邊環境，車程約3分鐘即可抵達學區樂善國小、文青雙語國中小學，距大崗國中約7分鐘車程，車程約4分鐘可至滯洪池公園，距林口綜合體育館約5分鐘車程，生活採買方面，車程約6~7分鐘可達頂好超市、全聯福利中心，距龜山黃昏市場約10分鐘車程。"/>
+    <n v="0.33900000000000002"/>
+    <n v="0.33900000000000002"/>
+    <s v="1幢，1棟，87戶一般事務所，3戶店面，45戶住家"/>
+    <n v="87"/>
+    <n v="3"/>
+    <n v="0.50270000000000004"/>
+    <n v="0.50270000000000004"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式49個"/>
+    <s v="30元/坪/月"/>
+    <s v="1:0.36"/>
+    <n v="0.36"/>
+    <s v="RC"/>
+    <s v="332.5坪"/>
+    <n v="332.5"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <m/>
+    <m/>
+    <s v="110桃市都建執照字第00147號"/>
+    <s v="王成維建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="314"/>
+    <s v="3.中心商業區"/>
+    <s v="大亮 泊"/>
+    <x v="28"/>
+    <s v="fig/AiCity-939-大亮泊.webp"/>
+    <s v="https://market.591.com.tw/5855860"/>
+    <n v="33.700000000000003"/>
+    <s v="610/585"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="38-40 萬/坪"/>
+    <n v="38"/>
+    <n v="40"/>
+    <n v="2"/>
+    <n v="39"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="185萬"/>
+    <n v="185"/>
+    <n v="185"/>
+    <n v="0.8"/>
+    <s v="銷售中"/>
+    <s v="2026年6月"/>
+    <x v="8"/>
+    <s v="2026Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(18~20坪), 三房(26坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住家用"/>
+    <s v="桃園市龜山區文化一路"/>
+    <s v="桃園市龜山區文化一路與文青路口"/>
+    <m/>
+    <s v="大亮建築"/>
+    <s v="大亮建築"/>
+    <s v="大亮營造股份有限公司"/>
+    <s v="大亮建築股份有限公司"/>
+    <m/>
+    <n v="0.33900000000000002"/>
+    <n v="0.33900000000000002"/>
+    <s v="_x000a_1幢，4棟，568戶住家，17戶店面"/>
+    <n v="568"/>
+    <n v="17"/>
+    <n v="0.63100000000000001"/>
+    <n v="0.63100000000000001"/>
+    <s v="地上29層,地下6層"/>
+    <n v="29"/>
+    <s v="平面式701個、預留管線"/>
+    <s v="50元/坪/月"/>
+    <s v="1:0.56"/>
+    <n v="0.56000000000000005"/>
+    <s v="RC"/>
+    <s v="2214坪"/>
+    <n v="2214"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="401"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="竹城甲子園"/>
+    <x v="29"/>
+    <s v="fig/AiCity-939-竹城甲子園.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=119261&amp;v=720"/>
+    <n v="26.45"/>
+    <s v="104/1209"/>
+    <n v="28.89"/>
+    <n v="22.46"/>
+    <s v="26~28萬元/坪"/>
+    <n v="26"/>
+    <n v="28"/>
+    <n v="27"/>
+    <n v="1"/>
+    <s v="38~41 萬/坪"/>
+    <n v="38"/>
+    <n v="41"/>
+    <n v="3"/>
+    <n v="39.5"/>
+    <m/>
+    <s v="竹城甲子園住戶交流區"/>
+    <s v="https://www.facebook.com/groups/1127911624065990"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年下半度"/>
+    <x v="3"/>
+    <s v="2021Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(26~28坪) 、三房(36~39坪) 、四房(43~49坪) 、2+1房(26~29坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化一路、文桃路口"/>
+    <s v="桃園市龜山區文化一路588號"/>
+    <s v="竹城建設股份有限公司"/>
+    <s v="竹城建設"/>
+    <s v="竹城建設"/>
+    <s v="大裕營造有限公司"/>
+    <s v="海悅國際開發股份有限公司"/>
+    <s v="近捷運、景觀宅、近公園、重劃區"/>
+    <s v="32.5%"/>
+    <n v="0.32500000000000001"/>
+    <s v="8棟，1144戶住家，30戶店面，33戶一般事務所，2戶商場"/>
+    <n v="1144"/>
+    <n v="30"/>
+    <s v="50.21%"/>
+    <n v="0.50209999999999999"/>
+    <s v="地上24層，地下4層"/>
+    <n v="24"/>
+    <s v="平面式1063個"/>
+    <s v="待定"/>
+    <s v="1:0.88"/>
+    <n v="0.88"/>
+    <s v="RC"/>
+    <s v="4352.46坪"/>
+    <n v="4352.46"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜01249-02號等1個"/>
+    <s v="閤康聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="402"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="金捷市"/>
+    <x v="30"/>
+    <s v="fig/AiCity-939-金捷市.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116107&amp;v=720"/>
+    <n v="26.46"/>
+    <n v="24.18"/>
+    <n v="29.57"/>
+    <n v="21.5"/>
+    <s v="30.5萬元/坪"/>
+    <n v="30.5"/>
+    <n v="30.5"/>
+    <n v="30.5"/>
+    <n v="0"/>
+    <s v="30.5萬元/坪"/>
+    <n v="30.5"/>
+    <n v="30.5"/>
+    <n v="0"/>
+    <n v="30.5"/>
+    <m/>
+    <s v="金捷市準鄰居交流園地"/>
+    <s v="https://www.facebook.com/groups/238626460426128"/>
+    <m/>
+    <s v="140~215萬"/>
+    <n v="140"/>
+    <n v="215"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="2"/>
+    <s v="2020Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(26坪)、三房(38坪)、1+1房(26坪)、2+1房(34坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文化一路"/>
+    <s v="桃園市龜山區文化一路"/>
+    <s v="鴻築建設股份有限公司"/>
+    <s v="鴻築建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="漢森廣告事業有限公司"/>
+    <s v="近捷運、明星學區、制震宅、近公園、重劃區"/>
+    <s v="31.9%"/>
+    <n v="0.31900000000000001"/>
+    <s v="4幢，754戶住家，23戶店面, 1商場"/>
+    <n v="754"/>
+    <n v="23"/>
+    <s v="50.74%"/>
+    <n v="0.50739999999999996"/>
+    <s v="地上28層，地下6層"/>
+    <n v="28"/>
+    <s v="平面式822個"/>
+    <s v="待定"/>
+    <s v="1:1.06"/>
+    <n v="1.06"/>
+    <s v="RC"/>
+    <s v="2090.31坪"/>
+    <n v="2090.31"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜00822號等1個"/>
+    <s v="拓樸聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="403"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="捷市達"/>
+    <x v="31"/>
+    <s v="fig/AiCity-939-鴻築捷市達.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122649&amp;v=720"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="35~38萬元/坪"/>
+    <n v="35"/>
+    <n v="38"/>
+    <n v="36.5"/>
+    <n v="1.5"/>
+    <s v="45~48 萬/坪"/>
+    <n v="45"/>
+    <n v="48"/>
+    <n v="3"/>
+    <n v="46.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="175~205萬"/>
+    <n v="175"/>
+    <n v="205"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2023年12月"/>
+    <x v="4"/>
+    <s v="2025Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(23、28坪) 、三房(33坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區善捷段182地號"/>
+    <s v="桃園市龜山區文化一路238號旁"/>
+    <s v="鴻築建設股份有限公司"/>
+    <s v="鴻築建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="漢林廣告事業有限公司"/>
+    <s v="近捷運、景觀宅、制震宅、近公園、重劃區"/>
+    <s v="32%"/>
+    <n v="0.32"/>
+    <s v="1幢，4棟，771戶住家，31戶店面，1戶商場"/>
+    <n v="771"/>
+    <n v="31"/>
+    <s v="49.53%"/>
+    <n v="0.49530000000000002"/>
+    <s v="地上29層，地下5層"/>
+    <n v="29"/>
+    <s v="平面式778個"/>
+    <s v="待定"/>
+    <s v="1:0.97"/>
+    <n v="0.97"/>
+    <s v="RC"/>
+    <s v="2067.24坪"/>
+    <n v="2067.2399999999998"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00438-01號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="404"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="詠勝市中欣"/>
+    <x v="32"/>
+    <s v="fig/AiCity-939-詠勝市中欣.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=120096&amp;v=720"/>
+    <n v="21.19"/>
+    <n v="32.74"/>
+    <n v="48.58"/>
+    <n v="19.559999999999999"/>
+    <s v="27~32萬元/坪"/>
+    <n v="27"/>
+    <n v="32"/>
+    <n v="29.5"/>
+    <n v="2.5"/>
+    <s v="24~25 萬/坪"/>
+    <n v="24"/>
+    <n v="25"/>
+    <n v="1"/>
+    <n v="24.5"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="155~205萬"/>
+    <n v="155"/>
+    <n v="205"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2022年12月"/>
+    <x v="5"/>
+    <s v="2023Q1"/>
+    <s v="標準配備"/>
+    <s v="一房(20坪) 、二房(25坪) 、三房(28~37坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂善一路"/>
+    <s v="桃園市龜山區樂善一路、樂善二路口"/>
+    <s v="詠勝開發有限公司"/>
+    <s v="詠勝開發"/>
+    <s v="詠勝開發"/>
+    <s v="詠勝開發營造股份有限公司"/>
+    <s v="君漾廣告有限公司"/>
+    <s v="近捷運、明星學區、景觀宅、近公園、重劃區、創意空間、低首付"/>
+    <s v="33%"/>
+    <n v="0.33"/>
+    <s v="1棟，257戶住家，7戶店面，32戶一般事務所"/>
+    <n v="257"/>
+    <n v="7"/>
+    <s v="53.26%"/>
+    <n v="0.53259999999999996"/>
+    <s v="地上22層，地下5層"/>
+    <n v="22"/>
+    <s v="平面式298個"/>
+    <s v="待定"/>
+    <s v="1:1.01"/>
+    <n v="1.01"/>
+    <s v="RC"/>
+    <s v="926.66坪"/>
+    <n v="926.66"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜00159-01號等1個"/>
+    <s v="新森峰建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="405"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="新A7"/>
+    <x v="33"/>
+    <s v="fig/AiCity-939-新A7.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122651"/>
+    <n v="26.59"/>
+    <s v="130/374"/>
+    <n v="31.65"/>
+    <n v="24.01"/>
+    <s v="31~33萬元/坪"/>
+    <n v="31"/>
+    <n v="33"/>
+    <n v="32"/>
+    <n v="1"/>
+    <s v="32~35 萬/坪"/>
+    <n v="32"/>
+    <n v="35"/>
+    <n v="3"/>
+    <n v="33.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="180~200萬"/>
+    <n v="180"/>
+    <n v="200"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年第四季度"/>
+    <x v="0"/>
+    <s v="2022Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(23~27坪) 、三房(25~38坪) 、四房(44~46坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂善二路 "/>
+    <s v="桃園市龜山區文化一路115號 "/>
+    <s v="鴻廣建設股份有限公司"/>
+    <s v="鴻廣建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="達程廣告股份有限公司"/>
+    <s v="近捷運、明星學區、近公園、重劃區"/>
+    <n v="0.32"/>
+    <n v="0.32"/>
+    <s v="4幢，7棟，371戶住家，3戶店面"/>
+    <n v="371"/>
+    <n v="3"/>
+    <n v="0.46450000000000002"/>
+    <n v="0.46450000000000002"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式143個、機械式232個"/>
+    <s v="待定"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="1538.68坪"/>
+    <n v="1538.68"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00568-02號"/>
+    <s v="張建鴻建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="406"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="富御捷境"/>
+    <x v="34"/>
+    <s v="fig/AiCity-939-富御捷境.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=116475"/>
+    <n v="25.73"/>
+    <n v="23.14"/>
+    <n v="31.69"/>
+    <n v="19.95"/>
+    <s v="27~29萬元/坪"/>
+    <n v="27"/>
+    <n v="29"/>
+    <n v="28"/>
+    <n v="1"/>
+    <s v="30~32 萬/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <n v="2"/>
+    <n v="31"/>
+    <m/>
+    <s v="A7 富御捷境好鄰居交流團"/>
+    <s v="https://www.facebook.com/groups/1970564956581068"/>
+    <m/>
+    <s v="195~200萬"/>
+    <n v="195"/>
+    <n v="200"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="2"/>
+    <s v="2020Q2"/>
+    <s v="標準配備"/>
+    <s v="一房(18.78坪)、二房(22~29坪)、三房(37~41坪)、四房(43坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區善捷段地號 142"/>
+    <s v="桃園市龜山區文桃路"/>
+    <s v="和峻建設股份有限公司"/>
+    <s v="和峻建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="新理想廣告有限公司"/>
+    <s v="近捷運、景觀宅、重劃區"/>
+    <s v="31.5%"/>
+    <n v="0.315"/>
+    <s v="5棟，337戶住家，2戶店面"/>
+    <n v="337"/>
+    <n v="2"/>
+    <s v="47.5%"/>
+    <n v="0.47499999999999998"/>
+    <s v="地上14~15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式180個、機械式125個"/>
+    <s v="待定"/>
+    <s v="1:0.9"/>
+    <n v="0.9"/>
+    <s v="RC"/>
+    <s v="1359.03坪"/>
+    <n v="1359.03"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜01237 號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="407"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="富宇哈佛苑"/>
+    <x v="35"/>
+    <s v="fig/AiCity-939-富宇哈佛苑.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121157&amp;v=720"/>
+    <n v="34.08"/>
+    <s v="89/491"/>
+    <n v="41.77"/>
+    <n v="22.76"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <n v="35.5"/>
+    <n v="2.5"/>
+    <s v="44~49 萬/坪"/>
+    <n v="44"/>
+    <n v="49"/>
+    <n v="5"/>
+    <n v="46.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="180~205萬"/>
+    <n v="180"/>
+    <n v="205"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2023年第四季"/>
+    <x v="5"/>
+    <s v="2023Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(22~25坪) 、三房(30~37坪) 、2+1房(27坪) 、3+1房(40坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區善捷段75地號"/>
+    <s v="桃園市龜山區文化一路、華亞三路"/>
+    <s v="富宇建設股份有限公司"/>
+    <s v="富宇建設"/>
+    <s v="富宇建設"/>
+    <s v="盛傑營造有限公司"/>
+    <s v="華昱廣告有限公司"/>
+    <s v="近捷運、明星學區、景觀宅、近公園、重劃區、低首付"/>
+    <s v="33.5%"/>
+    <n v="0.33500000000000002"/>
+    <s v="1幢，3棟，483戶住家，8戶店面"/>
+    <n v="483"/>
+    <n v="8"/>
+    <s v="44.18%"/>
+    <n v="0.44180000000000003"/>
+    <s v="地上24層，地下4層"/>
+    <n v="24"/>
+    <s v="平面式495個"/>
+    <s v="70元/坪/月"/>
+    <s v="1:1.01"/>
+    <n v="1.01"/>
+    <s v="RC"/>
+    <s v="2155.85坪"/>
+    <n v="2155.85"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00961號等1個"/>
+    <s v="吳六合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="408"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="頤昌豐岳"/>
+    <x v="36"/>
+    <s v="fig/AiCity-939-頤昌豐岳.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/info?hid=122055"/>
+    <m/>
+    <n v="24.99"/>
+    <n v="27.76"/>
+    <n v="22.52"/>
+    <s v="30萬元/坪"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <s v="30萬元/坪"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="30"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="160~190萬"/>
+    <n v="160"/>
+    <n v="190"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2022年第一季度"/>
+    <x v="0"/>
+    <s v="2022Q1"/>
+    <s v="標準配備"/>
+    <s v="二房(26~28坪) 、三房(38~40坪) 、四房(45~52坪) 、店面(36~52坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文樂路、樂善一路交叉口附近"/>
+    <s v="桃園市龜山區文樂路、樂善一路交叉口附近"/>
+    <s v="頤昌建設股份有限公司"/>
+    <s v="頤昌建設"/>
+    <s v="頤昌建設"/>
+    <s v="晉福營造"/>
+    <s v="鈞驛廣告"/>
+    <s v="近捷運、明星學區、重劃區"/>
+    <n v="0.32"/>
+    <n v="0.32"/>
+    <s v="2棟，154戶住家，9戶店面"/>
+    <n v="154"/>
+    <n v="9"/>
+    <n v="0.4622"/>
+    <n v="0.4622"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式190個"/>
+    <s v="待定"/>
+    <s v="1:1.17"/>
+    <n v="1.17"/>
+    <s v="RC"/>
+    <s v="933.78坪"/>
+    <n v="933.78"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第01005-01號"/>
+    <s v="陳朝雄建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="409"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="新未來2"/>
+    <x v="37"/>
+    <s v="fig/AiCity-939-新未來2.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/info?hid=118904"/>
+    <m/>
+    <n v="26.39"/>
+    <n v="29.56"/>
+    <n v="23.12"/>
+    <s v="30~32萬元/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <n v="31"/>
+    <n v="1"/>
+    <s v="30~32萬元/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <n v="2"/>
+    <n v="31"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="180~210萬"/>
+    <n v="180"/>
+    <n v="210"/>
+    <n v="0.75"/>
+    <s v="銷售中"/>
+    <s v="2022年5月"/>
+    <x v="0"/>
+    <s v="2022Q2"/>
+    <s v="標準配備"/>
+    <s v="三房(36~42坪) 、四房(54坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文桃路內"/>
+    <s v="桃園市龜山區樂善一路10號 "/>
+    <s v="遠雄建設事業股份有限公司"/>
+    <s v="遠雄建設"/>
+    <s v="遠雄建設"/>
+    <s v="遠雄營造股份有限公司"/>
+    <s v="遠雄房地產發展(股)公司"/>
+    <s v="近捷運、明星學區、近公園、重劃區"/>
+    <n v="0.33"/>
+    <n v="0.33"/>
+    <s v="2棟，376戶住家，9戶店面"/>
+    <n v="376"/>
+    <n v="9"/>
+    <n v="0.36220000000000002"/>
+    <n v="0.36220000000000002"/>
+    <s v="地上22層，地下4層"/>
+    <n v="22"/>
+    <s v="平面式438個"/>
+    <s v="待定"/>
+    <s v="1:1.14"/>
+    <n v="1.1399999999999999"/>
+    <s v="RC"/>
+    <s v="1955.56坪"/>
+    <n v="1955.56"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(107)桃市字第會龜00687號"/>
+    <s v="李祖原聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="410"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="新未來3"/>
+    <x v="38"/>
+    <s v="fig/AiCity-939-新未來3.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/info?hid=122831"/>
+    <n v="30.02"/>
+    <n v="29.48"/>
+    <n v="32"/>
+    <n v="25.65"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <n v="35.5"/>
+    <n v="2.5"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <n v="5"/>
+    <n v="35.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="190萬"/>
+    <n v="190"/>
+    <n v="190"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2023年12月"/>
+    <x v="5"/>
+    <s v="2023Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(24~27坪) 、2+1房(36~42坪) 、3+1房(46坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文吉路及樂善二路路口"/>
+    <s v="桃園市龜山區樂善一路10號 "/>
+    <s v="遠雄建設事業股份有限公司"/>
+    <s v="遠雄建設"/>
+    <s v="遠雄建設"/>
+    <s v="遠雄營造股份有限公司"/>
+    <s v="遠雄房地產發展(股)公司"/>
+    <s v="近捷運、明星學區、近公園、重劃區"/>
+    <n v="0.3327"/>
+    <n v="0.3327"/>
+    <s v="2幢，3棟，582戶住家，16戶店面"/>
+    <n v="582"/>
+    <n v="16"/>
+    <n v="0.38300000000000001"/>
+    <n v="0.38300000000000001"/>
+    <s v="地上19、22層，地下5層"/>
+    <n v="22"/>
+    <s v="平面式598個"/>
+    <s v="待定"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="2513.22坪"/>
+    <n v="2513.2199999999998"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="109桃市都建執照字第00076號"/>
+    <s v="三門聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="411"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="和洲金剛"/>
+    <x v="39"/>
+    <s v="fig/AiCity-939-和洲金剛.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=122486&amp;v=720"/>
+    <n v="26.33"/>
+    <s v="143/221"/>
+    <n v="28.67"/>
+    <n v="21.01"/>
+    <s v="25~27萬元/坪"/>
+    <n v="25"/>
+    <n v="27"/>
+    <n v="26"/>
+    <n v="1"/>
+    <s v="30~32 萬/坪"/>
+    <n v="30"/>
+    <n v="32"/>
+    <n v="2"/>
+    <n v="31"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="待定"/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2021年第四季"/>
+    <x v="0"/>
+    <s v="2022Q1"/>
+    <s v="標準配備"/>
+    <s v="二房(26~30坪) 、三房(36~40坪) 、四房(47坪) 、1+1房(16坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂善二路"/>
+    <s v="桃園市龜山區文化一路、樂善路口"/>
+    <s v="和洲建設股份有限公司"/>
+    <s v="和洲建設"/>
+    <s v="寶佳集團"/>
+    <s v="國城營造有限公司"/>
+    <s v="君翊行銷-翊鼎國際"/>
+    <s v="近捷運、明星學區、制震宅、近公園、重劃區"/>
+    <s v="32%"/>
+    <n v="0.32"/>
+    <s v="3幢，3棟，210戶住家，11戶店面"/>
+    <n v="210"/>
+    <n v="11"/>
+    <s v="45.54%"/>
+    <n v="0.45540000000000003"/>
+    <s v="地上15層，地下3~4層"/>
+    <n v="15"/>
+    <s v="平面式226個"/>
+    <s v="待定"/>
+    <s v="1:1.02"/>
+    <n v="1.02"/>
+    <s v="RC"/>
+    <s v="1359.03坪"/>
+    <n v="1359.03"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <s v="國原保全"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00611號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="412"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="君邑丘比特"/>
+    <x v="40"/>
+    <s v="fig/AiCity-939-邱比特.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121781&amp;"/>
+    <n v="27.47"/>
+    <s v="165/178"/>
+    <n v="32.229999999999997"/>
+    <n v="22.94"/>
+    <s v="27.8~32萬元/坪"/>
+    <n v="27.8"/>
+    <n v="32"/>
+    <n v="29.9"/>
+    <n v="2.1000000000000014"/>
+    <s v="29.8~38.2 萬/坪"/>
+    <n v="29.8"/>
+    <n v="38.200000000000003"/>
+    <n v="8.4000000000000021"/>
+    <n v="34"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="180~230萬"/>
+    <n v="180"/>
+    <n v="230"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2022年上半年"/>
+    <x v="0"/>
+    <s v="2022Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(25~28坪) 、三房(38~40坪) 、四房(47坪) 、3+1房(46坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住家用"/>
+    <s v="桃園市龜山區文吉路"/>
+    <s v="桃園市龜山區文桃路 "/>
+    <s v="君悅建設有限公司"/>
+    <s v="君悅建設"/>
+    <s v="君悅建設"/>
+    <s v="捷堡營造工程有限公司"/>
+    <s v="捷堡營造工程有限公司"/>
+    <s v="近捷運、明星學區、景觀宅、制震宅、近公園、重劃區、低首付"/>
+    <s v="32.46~33.79%"/>
+    <n v="0.33129999999999998"/>
+    <s v="1幢，4棟，173戶住家，5戶店面"/>
+    <n v="173"/>
+    <n v="5"/>
+    <n v="0.46150000000000002"/>
+    <n v="0.46150000000000002"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式190個"/>
+    <s v="待定"/>
+    <s v="1:1.07"/>
+    <n v="1.07"/>
+    <s v="RC"/>
+    <s v="1030.74坪"/>
+    <n v="1030.74"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00488-01號等1個"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="413"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="頤昌璞岳"/>
+    <x v="41"/>
+    <s v="fig/AiCity-939-頤昌璞岳.jpeg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=124978"/>
+    <n v="27.11"/>
+    <n v="26.83"/>
+    <n v="34.42"/>
+    <n v="24.79"/>
+    <s v="32~33 萬/坪"/>
+    <n v="32"/>
+    <n v="33"/>
+    <n v="32.5"/>
+    <n v="0.5"/>
+    <s v="32~33 萬/坪"/>
+    <n v="32"/>
+    <n v="33"/>
+    <n v="1"/>
+    <n v="32.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="待定"/>
+    <m/>
+    <m/>
+    <s v="待定"/>
+    <s v="已完銷"/>
+    <s v="2022年第三季度"/>
+    <x v="0"/>
+    <s v="2022Q3"/>
+    <s v="標準配備"/>
+    <s v="二房(27~29坪) 、 三房(36~39坪) 、 四房(45坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住家用"/>
+    <s v="桃園市龜山區樂捷段253地號"/>
+    <s v="桃園市龜山區文樂路、樂善一路交叉口附近 "/>
+    <s v="頤昌建設股份有限公司"/>
+    <s v="頤昌建設"/>
+    <s v="頤昌建設"/>
+    <s v="晉福營造有限公司"/>
+    <s v="鈞驛廣告"/>
+    <s v="周邊環境，基地鄰近文青雙語中小學(預定地)，車程7分鐘可至A8長庚商圈，生活採買方面，車程4分鐘可達頂好超市，距全聯(林口復興店)約8分鐘車程。交通方面，車程5分鐘可至機場捷運A7體育大學站，亦有國道一號林口交流道可利用。"/>
+    <n v="0.32100000000000001"/>
+    <n v="0.32100000000000001"/>
+    <s v="1幢，2棟，124戶住家，11戶店面"/>
+    <n v="124"/>
+    <n v="11"/>
+    <n v="0.51349999999999996"/>
+    <n v="0.51349999999999996"/>
+    <s v="地上14層，地下4層"/>
+    <n v="14"/>
+    <s v="平面式136個"/>
+    <s v="待定"/>
+    <s v="1:1.01"/>
+    <n v="1.01"/>
+    <s v="RC"/>
+    <s v="595.29坪"/>
+    <n v="595.29"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="109桃市都建執照字第00379-01號"/>
+    <s v="閤康聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="414"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="合謙學"/>
+    <x v="42"/>
+    <s v="fig/AiCity-939-合謙學.webp"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=126450"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="32~35 萬/坪"/>
+    <n v="32"/>
+    <n v="35"/>
+    <n v="33.5"/>
+    <n v="1.5"/>
+    <s v="35~42 萬/坪"/>
+    <n v="35"/>
+    <n v="42"/>
+    <n v="7"/>
+    <n v="38.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="待定"/>
+    <m/>
+    <m/>
+    <s v="待定"/>
+    <s v="銷售中"/>
+    <s v="2022年第二季度"/>
+    <x v="0"/>
+    <s v="2022Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(25坪) 、 三房(34~37坪) 、 2+1房(26坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住家用"/>
+    <s v="桃園市龜山區樂善一路與牛角坡路口"/>
+    <s v="桃園市龜山區樂善一路與牛角坡路口"/>
+    <s v="合謙建設股份有限公司"/>
+    <s v="合謙建設"/>
+    <s v="合謙建設"/>
+    <s v="洛城營造有限公司"/>
+    <s v="翰永興業股份有限公司"/>
+    <s v="寧靜本案位於A7新林口重劃區中的文青文教區內之住宅用地，採零店面無事務所設計，並以中小型基地開發打造出百餘戶社區，讓住家回歸最基本對寧靜且不複雜的需求。健康社區緊鄰18份坑溪保護區，讓您不出門在家即可享受猶如群樹環繞的森林芬多精本案全戶型標配VAF可變氣流條件環境控制系統，以醫療環境的使用思維有效過濾PM2.5，進而使乾淨空氣有效率且足量進入住家。"/>
+    <n v="0.32500000000000001"/>
+    <n v="0.32500000000000001"/>
+    <s v="1幢，2棟，106戶住家"/>
+    <n v="106"/>
+    <n v="0"/>
+    <n v="0.45660000000000001"/>
+    <n v="0.45660000000000001"/>
+    <s v="地上14層，地下4層"/>
+    <n v="14"/>
+    <s v="平面式96個"/>
+    <s v="70元/坪/月"/>
+    <s v="1:0.91"/>
+    <n v="0.91"/>
+    <s v="RC"/>
+    <s v="1030.74坪"/>
+    <n v="1030.74"/>
+    <s v="住家用"/>
+    <s v="第三種住宅區"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="416"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="維特魯威"/>
+    <x v="43"/>
+    <s v="fig/AiCity-939-維特魯威.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=128903"/>
+    <n v="31.65"/>
+    <s v="92/136"/>
+    <n v="38.68"/>
+    <n v="27.48"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="37.8~45.5 萬/坪"/>
+    <n v="37.799999999999997"/>
+    <n v="45.5"/>
+    <m/>
+    <n v="41.65"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="銷售中"/>
+    <s v="2024年第四季度"/>
+    <x v="6"/>
+    <s v="2024Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(27~30坪) 、 三房(33.5~41坪) 、 四房(46、47坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住商用"/>
+    <s v="桃園市龜山區文桃路、牛角坡路交叉口"/>
+    <s v="桃園市龜山區文吉路旁"/>
+    <s v="法邑建設有限公司"/>
+    <s v="法邑建設"/>
+    <s v="法邑建設"/>
+    <s v="捷堡營造工程有限公司"/>
+    <s v="埜揚廣告有限公司"/>
+    <m/>
+    <n v="0.33400000000000002"/>
+    <n v="0.33400000000000002"/>
+    <s v="1幢，1棟，123戶住家，3戶店面，10戶一般事務所"/>
+    <n v="123"/>
+    <n v="3"/>
+    <n v="0.37569999999999998"/>
+    <n v="0.37569999999999998"/>
+    <s v="地上28層，地下5層"/>
+    <n v="28"/>
+    <s v="平面式140個"/>
+    <s v="60元/坪/月"/>
+    <s v="1:1.02"/>
+    <n v="1.02"/>
+    <s v="RC"/>
+    <s v="586.6坪"/>
+    <n v="586.6"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <m/>
+    <m/>
+    <s v="106桃市都建執照字第01039-02號"/>
+    <s v="拓璞聯合建築師事務所"/>
+    <m/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="417"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="頤昌澄岳"/>
+    <x v="44"/>
+    <s v="fig/AiCity-939-頤昌澄岳.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=128885&amp;v=720"/>
+    <m/>
+    <n v="25.41"/>
+    <n v="25.92"/>
+    <n v="25.06"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="39~40 萬/坪"/>
+    <n v="39"/>
+    <n v="40"/>
+    <m/>
+    <n v="39.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="175~210萬"/>
+    <n v="175"/>
+    <n v="210"/>
+    <m/>
+    <s v="銷售中"/>
+    <s v="2024年第二季度"/>
+    <x v="6"/>
+    <s v="2024Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(23坪) 、 三房(29~38坪) 、 2+1房(25坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住商用"/>
+    <s v="桃園市龜山區樂學一路、樂學二路交叉口"/>
+    <s v="桃園市龜山區樂學二路、樂學三路交叉口"/>
+    <s v="頤昌建設股份有限公司"/>
+    <s v="頤昌建設"/>
+    <s v="頤昌建設"/>
+    <s v="晉福營造有限公司"/>
+    <s v="新理想廣告"/>
+    <m/>
+    <n v="0.33"/>
+    <n v="0.33"/>
+    <s v="1幢，2棟，140戶住家，8戶店面"/>
+    <n v="140"/>
+    <n v="8"/>
+    <n v="0.38429999999999997"/>
+    <n v="0.38429999999999997"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式145個"/>
+    <s v="待定"/>
+    <s v="1:0.97"/>
+    <n v="0.97"/>
+    <s v="RC"/>
+    <s v="665.31坪"/>
+    <n v="665.31"/>
+    <s v="住商用"/>
+    <s v="第五種住宅區"/>
+    <m/>
+    <m/>
+    <s v="110桃市都建執照字第00808號"/>
+    <s v="陳朝雄建築師事務所"/>
+    <m/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="418"/>
+    <s v="4.文青國小生活圈"/>
+    <s v="玄泰T1"/>
+    <x v="45"/>
+    <s v="fig/AiCity-939-玄泰T1.webp"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=128089"/>
+    <n v="27.3"/>
+    <s v="378/595"/>
+    <n v="36.26"/>
+    <n v="21.25"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="34~38 萬/坪"/>
+    <n v="34"/>
+    <n v="38"/>
+    <n v="36"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="160~230萬"/>
+    <n v="160"/>
+    <n v="230"/>
+    <m/>
+    <s v="銷售中"/>
+    <s v="2026年第一季度"/>
+    <x v="8"/>
+    <s v="2026Q1"/>
+    <s v="標準配備"/>
+    <s v="三房(36~42坪) 、 3+1房(45~49坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住商用"/>
+    <s v="桃園市龜山區善捷段62地號 "/>
+    <s v="桃園市龜山區文化一路、樂善二路"/>
+    <s v=" 群泰開發有限公司"/>
+    <s v="群泰開發"/>
+    <s v="群泰開發"/>
+    <s v="益盛營造股份有限公司"/>
+    <s v="天湛廣告"/>
+    <m/>
+    <n v="0.33"/>
+    <n v="0.33"/>
+    <s v="1幢，4棟，264戶住家，7戶店面，294戶事務所，30戶一般"/>
+    <n v="264"/>
+    <n v="7"/>
+    <n v="0.59189999999999998"/>
+    <n v="0.59189999999999998"/>
+    <s v="地上25層，地下5層"/>
+    <n v="25"/>
+    <s v="平面式596個"/>
+    <s v="80元/坪/月"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="1848.19坪"/>
+    <n v="1848.19"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <m/>
+    <m/>
+    <s v="110桃市都建執照字第00311-01號"/>
+    <m/>
+    <m/>
+    <s v="樂善里"/>
+  </r>
+  <r>
+    <n v="501"/>
+    <s v="5.合宜住宅區"/>
+    <s v="新未來1"/>
+    <x v="46"/>
+    <s v="fig/AiCity-939-新未來1.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=113056"/>
+    <n v="34.36"/>
+    <n v="30.58"/>
+    <n v="37.549999999999997"/>
+    <n v="26.75"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <n v="35.5"/>
+    <n v="2.5"/>
+    <s v="33~38萬元/坪"/>
+    <n v="33"/>
+    <n v="38"/>
+    <n v="5"/>
+    <n v="35.5"/>
+    <s v="Y"/>
+    <s v="A7 遠雄新未來1 幸福住戶討論區"/>
+    <s v="https://www.facebook.com/groups/254570162464632"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="已完銷"/>
+    <s v="2021年下半年"/>
+    <x v="3"/>
+    <s v="2021Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(28~32坪) 、三房(42~50坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區樂善一路10號 "/>
+    <s v="桃園市龜山區樂善一路10號 "/>
+    <s v="遠雄建設事業股份有限公司"/>
+    <s v="遠雄建設"/>
+    <s v="遠雄建設"/>
+    <s v="遠雄營造"/>
+    <s v="遠雄房地產"/>
+    <s v="近捷運、景觀宅、近公園、重劃區、低首付"/>
+    <n v="0.33"/>
+    <n v="0.33"/>
+    <s v="3棟，807戶住家，14戶店面，3個商場"/>
+    <n v="807"/>
+    <n v="14"/>
+    <n v="0.57020000000000004"/>
+    <n v="0.57020000000000004"/>
+    <s v="地上28層，地下5層"/>
+    <n v="28"/>
+    <s v="平面式648個、機械式84個"/>
+    <s v="60元/坪/月"/>
+    <s v="1:0.89"/>
+    <n v="0.89"/>
+    <s v="RC"/>
+    <s v="2890坪"/>
+    <n v="2890"/>
+    <s v="住商用"/>
+    <s v="中心商業區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(106)桃市都建執照字第會龜00035號"/>
+    <s v="原大聯合建築師事務所"/>
+    <s v="暫無"/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="502"/>
+    <s v="5.合宜住宅區"/>
+    <s v="富宇天匯"/>
+    <x v="47"/>
+    <s v="fig/AiCity-939-富宇天匯.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=121159&amp;v=720"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="39~43萬元/坪"/>
+    <n v="39"/>
+    <n v="43"/>
+    <n v="41"/>
+    <n v="2"/>
+    <s v="45~50 萬/坪"/>
+    <n v="45"/>
+    <n v="50"/>
+    <n v="5"/>
+    <n v="47.5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="160~205萬"/>
+    <n v="160"/>
+    <n v="205"/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="2023年第二季度"/>
+    <x v="5"/>
+    <s v="2023Q2"/>
+    <s v="標準配備"/>
+    <s v="二房(20.86坪) 、三房(34~38坪) 、2+1房(27~28坪) 、3+1房(40、41坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區善捷段287地號"/>
+    <s v="桃園縣龜山鄉文化一路、文青路旁"/>
+    <s v="富宇建設股份有限公司"/>
+    <s v="富宇建設"/>
+    <s v="富宇建設"/>
+    <s v="盛傑營造有限公司"/>
+    <s v="華昱廣告"/>
+    <s v="近捷運、景觀宅、近公園、重劃區、低首付"/>
+    <n v="0.33500000000000002"/>
+    <n v="0.33500000000000002"/>
+    <s v="2幢，4棟，266戶住家，4戶店面"/>
+    <n v="266"/>
+    <n v="4"/>
+    <n v="0.49540000000000001"/>
+    <n v="0.49540000000000001"/>
+    <s v="地上15層，地下4層"/>
+    <n v="15"/>
+    <s v="平面式260個、機械式18個"/>
+    <s v="70元/坪/月"/>
+    <s v="1:1.03"/>
+    <n v="1.03"/>
+    <s v="RC"/>
+    <s v="1471.38坪"/>
+    <n v="1471.38"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第01027號"/>
+    <s v="徐瑞燦建築師事務所"/>
+    <s v="暫無"/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="503"/>
+    <s v="5.合宜住宅區"/>
+    <s v="竹城明治"/>
+    <x v="48"/>
+    <s v="fig/AiCity-939-竹城明治.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=120762"/>
+    <n v="26.56"/>
+    <n v="26.09"/>
+    <n v="33.130000000000003"/>
+    <n v="22.2"/>
+    <s v="28~30萬元/坪"/>
+    <n v="28"/>
+    <n v="30"/>
+    <n v="29"/>
+    <n v="1"/>
+    <s v="28~30萬元/坪"/>
+    <n v="28"/>
+    <n v="30"/>
+    <n v="2"/>
+    <n v="29"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="銷售中"/>
+    <s v="隨時交屋"/>
+    <x v="2"/>
+    <s v="2020Q1"/>
+    <s v="標準配備"/>
+    <s v="二房(25~28坪) 、三房(34~40坪) 、四房(43坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文青路363號對面"/>
+    <s v="桃園市龜山區文青路378號"/>
+    <s v="竹城建設股份有限公司"/>
+    <s v="竹城建設"/>
+    <s v="竹城建設"/>
+    <s v="大裕營造有限公司"/>
+    <s v="自建自售"/>
+    <s v="近捷運、近公園、重劃區"/>
+    <n v="0.32"/>
+    <n v="0.32"/>
+    <s v="1幢，6棟，168戶住家，5戶店面"/>
+    <n v="168"/>
+    <n v="5"/>
+    <s v="45.56%"/>
+    <n v="0.4556"/>
+    <s v="地上13層，地下3層"/>
+    <n v="13"/>
+    <s v="平面式81個、機械式68個"/>
+    <s v="待定"/>
+    <s v="1:0.86"/>
+    <n v="0.86"/>
+    <s v="RC"/>
+    <s v="961.25坪"/>
+    <n v="961.25"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <s v="暫無"/>
+    <s v="暫無"/>
+    <s v="(107)桃市都建執照字第會龜00995-01號等1個"/>
+    <s v="徐瑞燦建築師事務所"/>
+    <s v="109桃市都施使字第龜00492號"/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="504"/>
+    <s v="5.合宜住宅區"/>
+    <s v="竹城宇治"/>
+    <x v="49"/>
+    <s v="fig/AiCity-939-竹城宇治.jpg"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=115863"/>
+    <m/>
+    <n v="24.13"/>
+    <n v="29.39"/>
+    <n v="22.11"/>
+    <s v="30 萬/坪 "/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <s v="30 萬/坪 "/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="30"/>
+    <s v="Y"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="170~185萬"/>
+    <n v="170"/>
+    <n v="185"/>
+    <s v="80%"/>
+    <s v="已完銷"/>
+    <s v="隨時交屋"/>
+    <x v="1"/>
+    <s v="2019Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(25坪) 、 三房(38坪) 、 2+1房(28坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文青路378號"/>
+    <s v="桃園市龜山區文青路378號"/>
+    <s v="竹城機構-仲城建設股份有限公司"/>
+    <s v="竹城建設"/>
+    <s v="竹城建設"/>
+    <s v=" 大裕營造有限公司"/>
+    <s v="竹城機構-仲城建設股份有限公司"/>
+    <s v="周邊環境，距學區為樂善國小車程7分鐘即可到達，大岡國中約車程10分鐘，生活採買可至全聯福利中心或龜山黃昏市場。交通方面車程10~15分鐘可到林口交流道，往來大台北地區便利，或者是可走青山路車程10分鐘連接新莊。"/>
+    <n v="0.315"/>
+    <n v="0.315"/>
+    <s v="3棟，103戶住家，6戶店面"/>
+    <n v="103"/>
+    <n v="6"/>
+    <n v="0.45700000000000002"/>
+    <n v="0.45700000000000002"/>
+    <s v="地上13層，地下3層"/>
+    <n v="13"/>
+    <s v="平面式82個"/>
+    <s v="80元/坪/月"/>
+    <s v="1:0.75"/>
+    <n v="0.75"/>
+    <s v="RC"/>
+    <s v="638.13坪"/>
+    <n v="638.13"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <m/>
+    <m/>
+    <s v="(106)桃市都建執照字第會龜01145 號等2個"/>
+    <s v="徐瑞燦建築師事務所"/>
+    <s v="(108)桃市都施使字第龜00515號"/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="505"/>
+    <s v="5.合宜住宅區"/>
+    <s v="櫻花澍"/>
+    <x v="50"/>
+    <s v="fig/AiCity-939-櫻花澍.webp"/>
+    <s v="https://newhouse.591.com.tw/home/housing/detail?hid=124447"/>
+    <n v="26.2"/>
+    <n v="26.09"/>
+    <n v="28.35"/>
+    <n v="24.04"/>
+    <s v="28~32 萬/坪"/>
+    <n v="28"/>
+    <n v="32"/>
+    <n v="30"/>
+    <n v="2"/>
+    <s v="28~32 萬/坪"/>
+    <n v="28"/>
+    <n v="32"/>
+    <n v="4"/>
+    <n v="30"/>
+    <s v="Y"/>
+    <s v="A7櫻花澍已購戶討論區"/>
+    <s v="https://www.facebook.com/groups/1271297159886163"/>
+    <m/>
+    <s v="165~195萬"/>
+    <n v="165"/>
+    <n v="195"/>
+    <s v="80%"/>
+    <s v="已完銷"/>
+    <s v="2021年第四季度"/>
+    <x v="0"/>
+    <s v="2022Q4"/>
+    <s v="標準配備"/>
+    <s v="二房(25坪) 、 三房(35坪)"/>
+    <s v="預售屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文青二路"/>
+    <s v="桃園市龜山區文青路179號1F "/>
+    <s v="櫻花建設股份有限公司"/>
+    <s v="櫻花建設"/>
+    <s v="櫻花建設"/>
+    <s v="國城營造有限公司"/>
+    <s v="新高思廣告有限公司"/>
+    <s v="學區方面，鄰近文青雙語國中小預定地，生活採買方面，步行4分鐘可達美廉社(龜山文青店)，車程10分鐘可至全聯福利中心(龜山興華店)。交通方面，步行8分鐘可至機捷A7體育大學站，亦有國道一號林口交流道可利用。"/>
+    <n v="0.32"/>
+    <n v="0.32"/>
+    <s v="1幢，2棟，106戶住家，2戶店面"/>
+    <n v="106"/>
+    <n v="2"/>
+    <n v="0.38140000000000002"/>
+    <n v="0.38140000000000002"/>
+    <s v="地上14層，地下4層"/>
+    <n v="14"/>
+    <s v="平面式108個"/>
+    <s v="65元/坪/月"/>
+    <s v="1:1"/>
+    <n v="1"/>
+    <s v="RC"/>
+    <s v="602.07坪"/>
+    <n v="602.07000000000005"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <m/>
+    <s v="暫無"/>
+    <s v="108桃市都建執照字第00713-01號"/>
+    <s v="張建鴻建築師事務所"/>
+    <s v="暫無"/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="506"/>
+    <s v="5.合宜住宅區"/>
+    <s v="和煦隆陞"/>
+    <x v="51"/>
+    <s v="fig/AiCity-939-和煦隆陞.jpg"/>
+    <s v="https://market.591.com.tw/104829"/>
+    <n v="32.270000000000003"/>
+    <n v="28.56"/>
+    <n v="33.619999999999997"/>
+    <n v="26.99"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="32.3萬元/坪"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="已完銷"/>
+    <s v="隨時交屋"/>
+    <x v="3"/>
+    <s v="2021Q1"/>
+    <s v="標準配備"/>
+    <s v="二房(27.45坪)、三房(32.22~39.85坪)"/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住商用"/>
+    <s v="桃園市龜山區文青二路8號"/>
+    <m/>
+    <m/>
+    <s v="隆陞建設"/>
+    <m/>
+    <s v="富祥營造"/>
+    <s v="富祥營造"/>
+    <m/>
+    <n v="0.32700000000000001"/>
+    <n v="0.32700000000000001"/>
+    <s v="1幢，3棟，18戶住家，1戶店面"/>
+    <n v="22"/>
+    <m/>
+    <n v="0.5897"/>
+    <n v="0.5897"/>
+    <s v="地上8層,地下2層"/>
+    <n v="8"/>
+    <m/>
+    <s v="75元/坪/月"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="394.41坪"/>
+    <n v="394.41"/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <m/>
+    <s v="有"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="511"/>
+    <s v="5.合宜住宅區"/>
+    <s v="遠雄文青"/>
+    <x v="52"/>
+    <s v="fig/AiCity-939-遠雄文青.jpg"/>
+    <s v="https://www.farglory-land.com.tw/leasehold/%E9%81%A0%E9%9B%84%E6%99%82%E4%BB%A3%E7%B8%BD%E9%83%A8-2/"/>
+    <n v="22.77"/>
+    <n v="22.81"/>
+    <n v="30.56"/>
+    <n v="11.84"/>
+    <s v="2021/8:22.7萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <s v="2021/8:22.7萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="15"/>
+    <s v="Y"/>
+    <s v="A7 遠雄文青 住戶討論區"/>
+    <s v="https://www.facebook.com/groups/675455015969962"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="已完銷"/>
+    <s v="隨時交屋"/>
+    <x v="9"/>
+    <s v="2016Q4"/>
+    <s v="標準配備"/>
+    <m/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文青路179號"/>
+    <s v="桃園市龜山區文青路179號"/>
+    <m/>
+    <s v="遠雄建設"/>
+    <s v="遠雄建設"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1272"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="RC"/>
+    <m/>
+    <m/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="512"/>
+    <s v="5.合宜住宅區"/>
+    <s v="皇翔歡喜城"/>
+    <x v="53"/>
+    <s v="fig/AiCity-939-皇翔歡喜城.jpg"/>
+    <s v="https://www.uppercity.tw/"/>
+    <n v="22.67"/>
+    <n v="22.7"/>
+    <n v="28.54"/>
+    <n v="12.94"/>
+    <s v="2021/8:20.0萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <s v="2021/8:20.0萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="15"/>
+    <s v="Y"/>
+    <s v="A7皇翔歡喜城"/>
+    <s v="https://www.facebook.com/groups/521969711190884"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="已完銷"/>
+    <s v="隨時交屋"/>
+    <x v="9"/>
+    <s v="2016Q4"/>
+    <s v="標準配備"/>
+    <m/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="園市龜山區文青二路9-11號"/>
+    <m/>
+    <m/>
+    <s v="皇翔建設"/>
+    <s v="皇翔建設"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1780"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="RC"/>
+    <m/>
+    <m/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="513"/>
+    <s v="5.合宜住宅區"/>
+    <s v="名軒快樂家"/>
+    <x v="54"/>
+    <s v="fig/AiCity-939-名軒快樂家.jpg"/>
+    <s v="https://www.advancetek.com.tw/%E7%86%B1%E9%8A%B7%E5%80%8B%E6%A1%88/%E5%90%8D%E8%BB%92%E5%BF%AB%E6%A8%82%E5%AE%B6%E5%90%88%E5%AE%9C%E4%BD%8F%E5%AE%85a7_c%E5%9F%BA%E5%9C%B0/"/>
+    <n v="22.41"/>
+    <n v="22.48"/>
+    <n v="27.8"/>
+    <n v="13.62"/>
+    <s v="2021/8:21.7萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <s v="2021/8:21.7萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="15"/>
+    <s v="Y"/>
+    <s v="名軒快樂家-住戶專區"/>
+    <s v="https://www.facebook.com/groups/671624019658641"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="已完銷"/>
+    <s v="隨時交屋"/>
+    <x v="9"/>
+    <s v="2016Q4"/>
+    <s v="標準配備"/>
+    <m/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文學路237-247號號"/>
+    <m/>
+    <m/>
+    <s v="名軒開發"/>
+    <s v="名軒開發"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="514"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="RC"/>
+    <m/>
+    <m/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="文青里"/>
+  </r>
+  <r>
+    <n v="514"/>
+    <s v="5.合宜住宅區"/>
+    <s v="麗寶快樂家"/>
+    <x v="55"/>
+    <s v="fig/AiCity-939-麗寶快樂家.jpg"/>
+    <s v="http://lihpao.com.tw/appropriate/build.html"/>
+    <n v="22.58"/>
+    <n v="22.58"/>
+    <n v="28.38"/>
+    <n v="14.83"/>
+    <s v="2021/8:21.0萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <s v="2021/8:21.0萬元/坪"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="15"/>
+    <s v="Y"/>
+    <s v="A7 麗寶快樂家社區~住戶專區"/>
+    <s v="https://www.facebook.com/groups/A7happyhome"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="80%"/>
+    <s v="已完銷"/>
+    <s v="隨時交屋"/>
+    <x v="9"/>
+    <s v="2016Q4"/>
+    <s v="標準配備"/>
+    <m/>
+    <s v="新成屋"/>
+    <s v="A7XLK"/>
+    <s v="住宅大樓 住商用"/>
+    <s v="桃園市龜山區文青一路12號"/>
+    <m/>
+    <m/>
+    <s v="麗寶建設"/>
+    <s v="麗寶建設"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="897"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="RC"/>
+    <m/>
+    <m/>
+    <s v="住商用"/>
+    <s v="第三種住宅區"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="文青里"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96BECB74-4624-C448-8F45-5CCE516EEC65}" name="樞紐分析表8" cacheId="46" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:A70" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="69">
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="57">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="9"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="30"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="67">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="52"/>
+    </i>
+    <i r="1">
+      <x v="53"/>
+    </i>
+    <i r="1">
+      <x v="54"/>
+    </i>
+    <i r="1">
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x v="40"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i r="1">
+      <x v="42"/>
+    </i>
+    <i r="1">
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="35"/>
+    </i>
+    <i r="1">
+      <x v="38"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="43"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4947,6 +9778,407 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0396BE0-844C-9046-9BAB-01EC190B62A7}">
+  <dimension ref="A3:A70"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="49" max="51" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="55" max="57" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="6" bestFit="1" customWidth="1"/>
+    <col min="59" max="60" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:1">
+      <c r="A3" s="29" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="30">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="31" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="31" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="31" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="31" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="30">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="31" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="31" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="31" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="30">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="31" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="31" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="31" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="31" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="31" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="31" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="31" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="31" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="30">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="31" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="31" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="31" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="31" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="31" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="31" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="31" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="31" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="31" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="30">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="31" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="31" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="31" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="31" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="31" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="31" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="31" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="31" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="31" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="31" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="31" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="31" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="31" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="31" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="30">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="31" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="31" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="31" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="31" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="31" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="31" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="31" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="30">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="31" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="31" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="31" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="30">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="31" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="31" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="31" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="31" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="31" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="30">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="31" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="31" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="30" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="31" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="30" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F05EA98-B5B7-7547-BED4-A618D76058F2}">
   <dimension ref="A1:BQ57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
